--- a/脚本/汇总脚本/DML/配置脚本管理/其它功能/资产基本信息维护/资产基本信息维护配置脚本.xlsx
+++ b/脚本/汇总脚本/DML/配置脚本管理/其它功能/资产基本信息维护/资产基本信息维护配置脚本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="710"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="710" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="规则配置表_中债" sheetId="1" r:id="rId1"/>
@@ -33837,7 +33837,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P742"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -33882,7 +33881,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="15" t="s">
         <v>2215</v>
       </c>
@@ -33912,7 +33911,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-803','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000403','compareValue','svrBussRepAssetCreditNonstdInfoDto.floatFactorFlag','==','01','当“是否有浮动因子”选择“是”时','E');</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12" t="s">
         <v>887</v>
       </c>
@@ -33939,7 +33938,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-002','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000712','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12" t="s">
         <v>1087</v>
       </c>
@@ -33969,7 +33968,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-243','ASSET_INFO_DETAIL_RULE_0000-B690A5B9-FE5B-4725-E053-045AA8C093EE','compareValue','svrBussRepAssetCreditNonstdInfoDto.basisType','==','99','当基准利率种类为“99 其他”时','E');</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="12" t="s">
         <v>889</v>
       </c>
@@ -33996,7 +33995,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-004','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000762','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
         <v>2227</v>
       </c>
@@ -34023,7 +34022,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-804','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000406','isNotEmpty','svrBussRepAssetCreditNonstdInfoDto.repContainType','','0','当“含权类型”不为空时','E');</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="12" t="s">
         <v>891</v>
       </c>
@@ -34050,7 +34049,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-006','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000802','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="12" t="s">
         <v>892</v>
       </c>
@@ -34077,7 +34076,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-009','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000842','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="15" t="s">
         <v>2269</v>
       </c>
@@ -34107,7 +34106,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-811','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000417','inArray','svrBussRepAssetCreditNonstdInfoDto.repContainType','==','01,04','当“含权类型”选择“01 发行人赎回选择权”或“04投资人回售选择权”时','E');</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="15" t="s">
         <v>2141</v>
       </c>
@@ -34137,7 +34136,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-794','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000384','inArray','svrBussRepAssetCreditNonstdInfoDto.repDeferredInterestType','==','02,03','当“递延利息条款类型”选择“02 有利息递延条款”或“03 非利息递延条款引起的递延”时','E');</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="12" t="s">
         <v>895</v>
       </c>
@@ -34164,7 +34163,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-012','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000862','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="12" t="s">
         <v>896</v>
       </c>
@@ -34191,7 +34190,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-015','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D075-E050-007F010077FD','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="15" t="s">
         <v>2245</v>
       </c>
@@ -34221,7 +34220,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-808','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000411','compareValue','svrBussRepAssetCreditNonstdInfoDto.repExerciseType','==','02','当“行权方式”选择“02 欧式期权”时','E');</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="15" t="s">
         <v>2254</v>
       </c>
@@ -34251,7 +34250,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-809','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000413','compareValue','svrBussRepAssetCreditNonstdInfoDto.repExerciseType','==','03','当“行权方式”选择“03 百慕大期权”时','E');</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="12" t="s">
         <v>899</v>
       </c>
@@ -34278,7 +34277,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-018','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000940','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="12" t="s">
         <v>900</v>
       </c>
@@ -34305,7 +34304,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-019','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000950','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="12" t="s">
         <v>901</v>
       </c>
@@ -34332,7 +34331,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-020','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000960','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="12" t="s">
         <v>902</v>
       </c>
@@ -34359,7 +34358,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-022','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000990','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="12" t="s">
         <v>903</v>
       </c>
@@ -34386,7 +34385,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-023','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001020','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="12" t="s">
         <v>904</v>
       </c>
@@ -34413,7 +34412,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-024','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001010','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="12" t="s">
         <v>905</v>
       </c>
@@ -34440,7 +34439,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-026','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001040','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="12" t="s">
         <v>906</v>
       </c>
@@ -34467,7 +34466,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-027','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001050','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="12" t="s">
         <v>907</v>
       </c>
@@ -34494,7 +34493,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-028','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001060','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="15" t="s">
         <v>2268</v>
       </c>
@@ -34554,7 +34553,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-322','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001092','compareValue','svrBussRepAssetCreditNonstdInfoDto.repFinancierType1','==','99','融资人类型（按规模划分）为99其他','E');</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="12" t="s">
         <v>910</v>
       </c>
@@ -34581,7 +34580,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-031','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000011','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="12" t="s">
         <v>911</v>
       </c>
@@ -34608,7 +34607,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-032','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB6-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="12" t="s">
         <v>912</v>
       </c>
@@ -34635,7 +34634,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-033','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000019','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="12" t="s">
         <v>913</v>
       </c>
@@ -34662,7 +34661,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-034','ASSET_INFO_DETAIL_RULE_0000-884827E5-DF35-D920-E050-007F010077GG','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="12" t="s">
         <v>914</v>
       </c>
@@ -34689,7 +34688,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-035','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000018','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="12" t="s">
         <v>915</v>
       </c>
@@ -34716,7 +34715,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-036','ASSET_INFO_DETAIL_RULE_0000-884827E5-DF35-D920-E050-007F010077JJ','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="12" t="s">
         <v>916</v>
       </c>
@@ -34743,7 +34742,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-037','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000017','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="12" t="s">
         <v>917</v>
       </c>
@@ -34770,7 +34769,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-040','ASSET_INFO_DETAIL_RULE_0000-833d5cc0-39b9-4a10-a0fa-e7d11e9f5665','inArray','svrBussRepDepositInfoDto.repAssetType','!=','1002,1003','','E');</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="12" t="s">
         <v>918</v>
       </c>
@@ -34800,7 +34799,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-041','ASSET_INFO_DETAIL_RULE_0000-d1590181-8bf4-461f-8707-b0fcc37081b0','compareValue','svrBussRepDepositInfoDto.repDepoType','!=','06','当“存款类型”要素不选择“06 结构性存款”时','E');</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="12" t="s">
         <v>919</v>
       </c>
@@ -34830,7 +34829,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-042','ASSET_INFO_DETAIL_RULE_0000-4aa8e379-5f9d-42b1-b735-e1be9deef53a','compareValue','svrBussRepDepositInfoDto.repDepoType','!=','06','当“存款类型”要素不选择“06 结构性存款”时','E');</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="12" t="s">
         <v>920</v>
       </c>
@@ -34860,7 +34859,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-043','ASSET_INFO_DETAIL_RULE_0000-1267feb5-fab0-4589-baf9-90489ce6f24a','compareValue','svrBussRepDepositInfoDto.repDepoType','==','06','当“存款类型”要素选择“06 结构性存款”时','E');</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="12" t="s">
         <v>921</v>
       </c>
@@ -34890,7 +34889,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-044','ASSET_INFO_DETAIL_RULE_0000-9289ced0-e594-4172-95d8-85aefe03989c','compareValue','svrBussRepDepositInfoDto.repDepoType','==','06','当“存款类型”要素选择“06 结构性存款”时','E');</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="12" t="s">
         <v>922</v>
       </c>
@@ -34917,7 +34916,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-045','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D122-F050-007F010077FD','inArray','svrBussRepAssetMngProdInfoDto.repAssetType','==','1705','','E');</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="12" t="s">
         <v>923</v>
       </c>
@@ -34947,7 +34946,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-046','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA0-D920-F050-007F010077FD','compareValueAsNumber','svrBussRepAssetMngProdInfoDto.tradeFeeRate','&gt;','0','当交易相关合计费率不为0时','E');</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="12" t="s">
         <v>924</v>
       </c>
@@ -34977,7 +34976,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-048','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF9F-D920-F050-007F010077FD','compareValueAsNumber','svrBussRepAssetMngProdInfoDto.truFeeRate','&gt;','0','当托管费率不为0时','E');</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="12" t="s">
         <v>925</v>
       </c>
@@ -35007,7 +35006,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-049','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF8F-D920-F050-007F010077FD','compareValue','svrBussRepAssetMngProdInfoDto.rateFlag','==','02','是否有预期收益率为否','E');</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="12" t="s">
         <v>926</v>
       </c>
@@ -35037,7 +35036,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-050','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF8A-D920-F050-007F010077FD','compareValue','svrBussRepAssetMngProdInfoDto.rateFlag','==','01','是否有预期收益率为是','E');</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="12" t="s">
         <v>927</v>
       </c>
@@ -35067,7 +35066,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-051','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA1-D920-F050-007F010077FD','compareValueAsNumber','svrBussRepAssetMngProdInfoDto.agencyFeeRate','&gt;','0','当中介服务机构合计费率不为0时','E');</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="12" t="s">
         <v>928</v>
       </c>
@@ -35097,7 +35096,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-052','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF9E-D920-F050-007F010077FD','compareValueAsNumber','svrBussRepAssetMngProdInfoDto.mgrFeeRate','&gt;','0','管理费率不为0','E');</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="12" t="s">
         <v>929</v>
       </c>
@@ -35127,7 +35126,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-053','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF8C-D920-F050-007F010077FD','compareValue','svrBussRepAssetMngProdInfoDto.rateFlag','==','02','是否有预期收益率为否','E');</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="12" t="s">
         <v>930</v>
       </c>
@@ -35157,7 +35156,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-054','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF9D-D920-F050-007F010077FD','compareValue','svrBussRepAssetMngProdInfoDto.proProperty','==','99','资管计划属性选择“99 其他”场合','E');</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="12" t="s">
         <v>931</v>
       </c>
@@ -35184,7 +35183,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-057','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA2-D920-E250-007F010077FD','inArray','assetType2','==','1701,1702,1703,1704,1705,1706','','E');</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="12" t="s">
         <v>932</v>
       </c>
@@ -35214,7 +35213,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-058','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E250-117F01006A13','compareValueAsNumber','svrBussRepOutInvestAgrInfoDto.tradeFeeRate','&gt;','0','当交易相关合计费率不为0时','E');</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="12" t="s">
         <v>933</v>
       </c>
@@ -35244,7 +35243,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-059','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF7A-D920-E250-117F010077FD','compareValueAsNumber','svrBussRepOutInvestAgrInfoDto.otherFeeRate','&gt;','0','当其他合计费率不为0时','E');</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="12" t="s">
         <v>934</v>
       </c>
@@ -35274,7 +35273,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-060','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA2-D920-E250-007F010077FD','compareValueAsNumber','svrBussRepAssetMngProdInfoDto.otherFeeRate','&gt;','0','当其他合计费率不为0时','E');</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="12" t="s">
         <v>935</v>
       </c>
@@ -35304,7 +35303,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-061','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-E250-117F010077FD','compareValueAsNumber','svrBussRepOutInvestAgrInfoDto.truFeeRate','&gt;','0','当托管费率不为0时','E');</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="12" t="s">
         <v>936</v>
       </c>
@@ -35334,7 +35333,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-062','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF79-D920-E250-117F010077FD','compareValueAsNumber','svrBussRepOutInvestAgrInfoDto.agencyFeeRate','&gt;','0','当中介服务机构合计费率不为0时','E');</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="12" t="s">
         <v>937</v>
       </c>
@@ -35364,7 +35363,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-063','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF35-D981-E251-117F01007914','compareValueAsNumber','svrBussRepOutInvestAgrInfoDto.mgrFeeRate','&gt;','0','管理费率不为0','E');</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="12" t="s">
         <v>938</v>
       </c>
@@ -35391,7 +35390,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-066','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D135-E150-007F010077FD','inArray','assetType2','==','1705','','E');</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="12" t="s">
         <v>939</v>
       </c>
@@ -35418,7 +35417,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-068','ASSET_INFO_DETAIL_RULE_0000-884817E5-DF81-D920-E150-007F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="12" t="s">
         <v>940</v>
       </c>
@@ -35445,7 +35444,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-069','ASSET_INFO_DETAIL_RULE_0000-884827E5-DF35-D920-E150-007F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="12" t="s">
         <v>941</v>
       </c>
@@ -35472,7 +35471,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-070','ASSET_INFO_DETAIL_RULE_0000-443E4A59-6810-5A9E-E150-007F01006A36','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="12" t="s">
         <v>942</v>
       </c>
@@ -35499,7 +35498,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-072','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF6C-D920-E150-107F01007SFD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="12" t="s">
         <v>943</v>
       </c>
@@ -35526,7 +35525,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-075','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF7H-D920-E136-007F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="12" t="s">
         <v>944</v>
       </c>
@@ -35553,7 +35552,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-078','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF82-D920-E150-007FD10077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="12" t="s">
         <v>945</v>
       </c>
@@ -35580,7 +35579,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-080','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF82-D920-E150-107FD10077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="12" t="s">
         <v>946</v>
       </c>
@@ -35607,7 +35606,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-082','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF82-D920-E250-307FD10077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="12" t="s">
         <v>947</v>
       </c>
@@ -35634,7 +35633,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-084','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF83-D920-E150-A07F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="12" t="s">
         <v>948</v>
       </c>
@@ -35661,7 +35660,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-086','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF84-D920-E150-007FD10077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="12" t="s">
         <v>949</v>
       </c>
@@ -35688,7 +35687,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-087','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF88-D920-E150-007F010077FD','inArray','assetType2','==','1701,1702,1703,1704,1705,1706','','E');</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="12" t="s">
         <v>950</v>
       </c>
@@ -35715,7 +35714,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-088','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF88-D920-E150-007F010877FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="12" t="s">
         <v>951</v>
       </c>
@@ -35742,7 +35741,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-089','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF88-D920-E150-107F010877FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="12" t="s">
         <v>952</v>
       </c>
@@ -35769,7 +35768,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-090','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF88-D920-E150-207F010877FD','inArray','assetType2','==','1701,1702,1703,1704,1705,1706','','E');</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="12" t="s">
         <v>953</v>
       </c>
@@ -35796,7 +35795,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-092','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF89-D920-E150-107F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="12" t="s">
         <v>954</v>
       </c>
@@ -35823,7 +35822,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-097','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF93-D920-E150-007F030077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="12" t="s">
         <v>955</v>
       </c>
@@ -35850,7 +35849,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-098','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF93-D920-E150-107F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="12" t="s">
         <v>956</v>
       </c>
@@ -35877,7 +35876,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-101','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF95-D920-E150-007F710077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="12" t="s">
         <v>957</v>
       </c>
@@ -35904,7 +35903,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-102','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF95-D920-E150-107F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="12" t="s">
         <v>958</v>
       </c>
@@ -35931,7 +35930,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-105','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF97-D920-E150-007F910077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="12" t="s">
         <v>959</v>
       </c>
@@ -35958,7 +35957,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-107','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF97-D920-E150-107F910077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="12" t="s">
         <v>960</v>
       </c>
@@ -35985,7 +35984,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-108','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000424','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="12" t="s">
         <v>961</v>
       </c>
@@ -36042,7 +36041,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-324','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001094','compareValue','svrBussRepAssetCreditNonstdInfoDto.repFinancierType2','==','99','融资人类型（按经济类型划分）为99其他','E');</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="12" t="s">
         <v>963</v>
       </c>
@@ -36099,7 +36098,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-323','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001093','compareValue','svrBussRepAssetCreditNonstdInfoDto.repFinancierType3','==','99','融资人类型（按技术领域划分）为99其他','E');</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="12" t="s">
         <v>886</v>
       </c>
@@ -36129,7 +36128,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-001','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000712','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','!=','01,02','“担保方式”不是“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="12" t="s">
         <v>888</v>
       </c>
@@ -36159,7 +36158,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-003','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000762','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','==','01,02','当“担保方式”选择“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="12" t="s">
         <v>967</v>
       </c>
@@ -36186,7 +36185,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-115','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000582','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="12" t="s">
         <v>890</v>
       </c>
@@ -36216,7 +36215,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-005','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000802','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','!=','01,02','“担保方式”不是“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="12" t="s">
         <v>969</v>
       </c>
@@ -36243,7 +36242,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-117','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000622','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="12" t="s">
         <v>893</v>
       </c>
@@ -36267,7 +36266,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-010','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000842','isNotEmpty','svrBussRepAssetCreditNonstdInfoDto.repGuaType','','','“担保方式”不为空时','E');</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="12" t="s">
         <v>894</v>
       </c>
@@ -36297,7 +36296,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-011','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000862','lessThanCharLength','svrBussRepAssetCreditNonstdInfoDto.repGuaType','==','0','“担保方式”为空时','E');</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="12" t="s">
         <v>972</v>
       </c>
@@ -36324,7 +36323,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-120','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000672','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="12" t="s">
         <v>973</v>
       </c>
@@ -36351,7 +36350,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-121','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000081','inArray','assetType2','!=','1205','','E');</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="12" t="s">
         <v>974</v>
       </c>
@@ -36378,7 +36377,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-122','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000090','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="12" t="s">
         <v>975</v>
       </c>
@@ -36405,7 +36404,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-123','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF24-D920-E050-007F010077FD','inArray','assetType2','==','2201','','E');</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="12" t="s">
         <v>976</v>
       </c>
@@ -36432,7 +36431,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-124','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF25-D920-E050-007F010077FD','inArray','assetType2','==','2202','','E');</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="12" t="s">
         <v>977</v>
       </c>
@@ -36459,7 +36458,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-125','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000108','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="12" t="s">
         <v>978</v>
       </c>
@@ -36486,7 +36485,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-126','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000118','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="12" t="s">
         <v>979</v>
       </c>
@@ -36513,7 +36512,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-127','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000128','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="12" t="s">
         <v>980</v>
       </c>
@@ -36540,7 +36539,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-128','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000138','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="12" t="s">
         <v>981</v>
       </c>
@@ -36567,7 +36566,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-129','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000148','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="12" t="s">
         <v>982</v>
       </c>
@@ -36594,7 +36593,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-130','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000168','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="12" t="s">
         <v>983</v>
       </c>
@@ -36621,7 +36620,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-131','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000178','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="12" t="s">
         <v>984</v>
       </c>
@@ -36648,7 +36647,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-132','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000186','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="12" t="s">
         <v>985</v>
       </c>
@@ -36675,7 +36674,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-133','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000204','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="12" t="s">
         <v>986</v>
       </c>
@@ -36702,7 +36701,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-134','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000196','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="12" t="s">
         <v>987</v>
       </c>
@@ -36729,7 +36728,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-135','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000214','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="12" t="s">
         <v>988</v>
       </c>
@@ -36756,7 +36755,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-136','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000234','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="12" t="s">
         <v>989</v>
       </c>
@@ -36783,7 +36782,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-137','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000264','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="12" t="s">
         <v>990</v>
       </c>
@@ -36810,7 +36809,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-138','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000274','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="12" t="s">
         <v>991</v>
       </c>
@@ -36837,7 +36836,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-139','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000284','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="12" t="s">
         <v>992</v>
       </c>
@@ -36864,7 +36863,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-140','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000294','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="12" t="s">
         <v>993</v>
       </c>
@@ -36891,7 +36890,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-142','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000334','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="12" t="s">
         <v>994</v>
       </c>
@@ -36918,7 +36917,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-143','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000324','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="12" t="s">
         <v>995</v>
       </c>
@@ -36945,7 +36944,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-144','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000344','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="12" t="s">
         <v>996</v>
       </c>
@@ -36972,7 +36971,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-145','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000354','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="12" t="s">
         <v>997</v>
       </c>
@@ -36999,7 +36998,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-146','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000364','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A114" s="12" t="s">
         <v>962</v>
       </c>
@@ -37029,7 +37028,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-110','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000502','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','==','03,04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="12" t="s">
         <v>999</v>
       </c>
@@ -37056,7 +37055,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-148','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000374','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="12" t="s">
         <v>1000</v>
       </c>
@@ -37083,7 +37082,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-149','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000394','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A117" s="12" t="s">
         <v>964</v>
       </c>
@@ -37113,7 +37112,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-112','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000542','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','!=','03,04','当“担保方式”不是“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A118" s="12" t="s">
         <v>965</v>
       </c>
@@ -37143,7 +37142,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-113','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000492','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','==','03,04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="12" t="s">
         <v>1003</v>
       </c>
@@ -37170,7 +37169,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-152','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000444','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A120" s="12" t="s">
         <v>966</v>
       </c>
@@ -37200,7 +37199,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-114','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000582','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','==','03,04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="15" t="s">
         <v>1181</v>
       </c>
@@ -37230,7 +37229,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-418','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A38','compareValue','svrBussRepOtherInvestTargetInfoDto.rateFlag','==','02','当是否有预期收益率为否时','E');</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="15" t="s">
         <v>1182</v>
       </c>
@@ -37260,7 +37259,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-419','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A37','compareValue','svrBussRepOtherInvestTargetInfoDto.rateFlag','==','01','当是否有预期收益率为是时','E');</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="15" t="s">
         <v>1192</v>
       </c>
@@ -37290,7 +37289,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-436','ASSET_INFO_DETAIL_RULE_0000-884827E5-DF35-D920-E050-007F010077JN','inArray','svrBussRepOtherInvestTargetInfoDto.rateFlag','==','01','是否有预期收益率为是时','E');</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="12" t="s">
         <v>1026</v>
       </c>
@@ -37320,7 +37319,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-175','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A29','compareValue','svrBussRepOtherInvestTargetInfoDto.inAssetType','==','99','当行内资产类别为其他时','E');</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="12" t="s">
         <v>1086</v>
       </c>
@@ -37440,7 +37439,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-298','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF63-D920-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.financierType2','==','99','融资人类型（按技术领域划分）为99其他','E');</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A129" s="12" t="s">
         <v>1005</v>
       </c>
@@ -37470,7 +37469,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-154','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D158-E050-007F010077FD','inArray','svrBussRepOtherInvestTargetInfoDto.guaType','!=','03,04','“担保方式”不是“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A130" s="12" t="s">
         <v>1006</v>
       </c>
@@ -37500,7 +37499,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-155','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D163-E050-007F010077FD','inArray','svrBussRepOtherInvestTargetInfoDto.guaType','!=','01,02','“担保方式”不是“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A131" s="12" t="s">
         <v>1007</v>
       </c>
@@ -37530,7 +37529,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-156','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D168-E050-007F010077FD','inArray','svrBussRepOtherInvestTargetInfoDto.guaType','==','03,04,05,99','“担保方式”不是“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="12" t="s">
         <v>1008</v>
       </c>
@@ -37554,7 +37553,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-157','ASSET_INFO_DETAIL_RULE_0000-223E4A49-6810-5A9E-E050-007F01006A18','isNotEmpty','svrBussRepOtherInvestTargetInfoDto.guaType','','','“担保方式”不为空时','E');</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="12" t="s">
         <v>1009</v>
       </c>
@@ -37578,7 +37577,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-158','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF57-D920-E050-007F010077FD','isNotEmpty','svrBussRepOtherInvestTargetInfoDto.guaType','','','“担保方式”不为空时','E');</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="12" t="s">
         <v>1010</v>
       </c>
@@ -37608,7 +37607,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-159','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D159-E050-007F010077FD','lessThanCharLength','svrBussRepOtherInvestTargetInfoDto.guaType','==','0','“担保方式”为空时','E');</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="12" t="s">
         <v>1011</v>
       </c>
@@ -37638,7 +37637,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-160','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D169-E050-007F010077FD','lessThanCharLength','svrBussRepOtherInvestTargetInfoDto.guaType','==','0','“担保方式”为空时','E');</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="12" t="s">
         <v>1012</v>
       </c>
@@ -37668,7 +37667,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-161','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF58-D920-E050-007F010077FD','lessThanCharLength','svrBussRepOtherInvestTargetInfoDto.guaType','==','0','“担保方式”为空时','E');</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A137" s="12" t="s">
         <v>1014</v>
       </c>
@@ -37698,7 +37697,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-163','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D153-E050-007F010077FD','inArray','svrBussRepOtherInvestTargetInfoDto.guaType','!=','03,04','当“担保方式”不是“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="12" t="s">
         <v>1015</v>
       </c>
@@ -37728,7 +37727,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-164','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D154-E050-007F010077FD','lessThanCharLength','svrBussRepOtherInvestTargetInfoDto.guaType','==','0','“担保方式”为空时','E');</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A139" s="12" t="s">
         <v>1016</v>
       </c>
@@ -37758,7 +37757,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-165','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D001-E050-007F010077FD','inArray','svrBussRepOtherInvestTargetInfoDto.guaType','==','03,04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A140" s="12" t="s">
         <v>1017</v>
       </c>
@@ -37788,7 +37787,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-166','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D150-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','03','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A141" s="12" t="s">
         <v>1018</v>
       </c>
@@ -37818,7 +37817,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-167','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D151-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A142" s="12" t="s">
         <v>1019</v>
       </c>
@@ -37848,7 +37847,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-168','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D006-E050-007F010077FD','inArray','svrBussRepOtherInvestTargetInfoDto.guaType','==','03,04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A143" s="12" t="s">
         <v>1020</v>
       </c>
@@ -37878,7 +37877,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-169','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D156-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','03','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A144" s="12" t="s">
         <v>1021</v>
       </c>
@@ -37908,7 +37907,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-170','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D157-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="12" t="s">
         <v>1031</v>
       </c>
@@ -37935,7 +37934,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-180','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF56-D920-E050-107F010077FD','inArray','assetType2','==','1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="12" t="s">
         <v>1032</v>
       </c>
@@ -37962,7 +37961,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-181','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D150-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="12" t="s">
         <v>1033</v>
       </c>
@@ -37989,7 +37988,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-182','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D151-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="12" t="s">
         <v>1034</v>
       </c>
@@ -38016,7 +38015,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-183','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D153-E050-007F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="12" t="s">
         <v>1035</v>
       </c>
@@ -38043,7 +38042,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-184','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D154-E050-007F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="12" t="s">
         <v>1036</v>
       </c>
@@ -38070,7 +38069,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-185','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D156-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="12" t="s">
         <v>1037</v>
       </c>
@@ -38097,7 +38096,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-186','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D157-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="12" t="s">
         <v>1038</v>
       </c>
@@ -38124,7 +38123,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-187','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D158-E050-007F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="12" t="s">
         <v>1039</v>
       </c>
@@ -38151,7 +38150,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-188','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D159-E050-007F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="12" t="s">
         <v>1040</v>
       </c>
@@ -38178,7 +38177,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-189','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D165-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="12" t="s">
         <v>1041</v>
       </c>
@@ -38205,7 +38204,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-190','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D166-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="12" t="s">
         <v>1042</v>
       </c>
@@ -38232,7 +38231,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-191','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D168-E050-007F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="12" t="s">
         <v>1043</v>
       </c>
@@ -38259,7 +38258,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-192','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D169-E050-007F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="12" t="s">
         <v>1044</v>
       </c>
@@ -38286,7 +38285,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-193','ASSET_INFO_DETAIL_RULE_0000-223E4A49-6810-5A9E-E050-007F01006A18','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="12" t="s">
         <v>1045</v>
       </c>
@@ -38313,7 +38312,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-194','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF57-D920-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="12" t="s">
         <v>1046</v>
       </c>
@@ -38340,7 +38339,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-195','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF58-D920-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="12" t="s">
         <v>1047</v>
       </c>
@@ -38367,7 +38366,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-196','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A28','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="12" t="s">
         <v>1048</v>
       </c>
@@ -38394,7 +38393,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-197','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-107F01006A28','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="12" t="s">
         <v>1049</v>
       </c>
@@ -38421,7 +38420,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-198','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A29','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="12" t="s">
         <v>1050</v>
       </c>
@@ -38448,7 +38447,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-199','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A35','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="12" t="s">
         <v>1051</v>
       </c>
@@ -38475,7 +38474,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-200','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A36','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="12" t="s">
         <v>1052</v>
       </c>
@@ -38502,7 +38501,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-201','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF89-D920-E050-407F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="12" t="s">
         <v>1053</v>
       </c>
@@ -38529,7 +38528,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-202','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A39','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="12" t="s">
         <v>1054</v>
       </c>
@@ -38556,7 +38555,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-203','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A40','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="12" t="s">
         <v>1055</v>
       </c>
@@ -38583,7 +38582,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-204','ASSET_INFO_DETAIL_RULE_0000-884827E5-DF35-D920-E050-007F010077JU','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="12" t="s">
         <v>1056</v>
       </c>
@@ -38610,7 +38609,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-205','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A41','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="12" t="s">
         <v>1057</v>
       </c>
@@ -38637,7 +38636,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-206','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A42','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="12" t="s">
         <v>1058</v>
       </c>
@@ -38664,7 +38663,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-207','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A43','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="12" t="s">
         <v>1059</v>
       </c>
@@ -38691,7 +38690,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-208','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A44','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="12" t="s">
         <v>1060</v>
       </c>
@@ -38718,7 +38717,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-209','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A45','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="12" t="s">
         <v>1061</v>
       </c>
@@ -38745,7 +38744,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-210','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A46','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="12" t="s">
         <v>1062</v>
       </c>
@@ -38772,7 +38771,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-211','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A47','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="12" t="s">
         <v>1063</v>
       </c>
@@ -38799,7 +38798,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-212','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A48','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="12" t="s">
         <v>1064</v>
       </c>
@@ -38826,7 +38825,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-213','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-107F01006A48','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="12" t="s">
         <v>1065</v>
       </c>
@@ -38853,7 +38852,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-214','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A49','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="12" t="s">
         <v>1066</v>
       </c>
@@ -38880,7 +38879,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-215','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-107F01006A49','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="12" t="s">
         <v>1067</v>
       </c>
@@ -38907,7 +38906,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-216','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A50','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="12" t="s">
         <v>1068</v>
       </c>
@@ -38934,7 +38933,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-217','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A51','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="12" t="s">
         <v>1069</v>
       </c>
@@ -38961,7 +38960,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-218','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A52','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="12" t="s">
         <v>1070</v>
       </c>
@@ -38988,7 +38987,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-219','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A53','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="12" t="s">
         <v>1074</v>
       </c>
@@ -39018,7 +39017,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-223','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF77-D920-F153-007F010077FD','compareValue','svrBussRepFundInfoDto.investStage','==','99','投资阶段为99其他','E');</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="12" t="s">
         <v>1071</v>
       </c>
@@ -39048,7 +39047,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-220','ASSET_INFO_DETAIL_RULE_0000-223E4A49-6810-5A9E-E053-007F01006A92','compareValue','svrBussRepFundInfoDto.isGovernFund','==','01','当是否属于政府投资基金为是时','E');</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="12" t="s">
         <v>1075</v>
       </c>
@@ -39078,7 +39077,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-224','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF7A-D920-F153-117F010078FD','compareValue','svrBussRepFundInfoDto.sharesType1','==','99','投资企业类型（规模）为99其他','E');</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="12" t="s">
         <v>1076</v>
       </c>
@@ -39108,7 +39107,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-225','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF7A-D920-F153-117F010079FD','compareValue','svrBussRepFundInfoDto.sharesType2','==','99','投资企业类型（经济类型）为99其他','E');</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="12" t="s">
         <v>1077</v>
       </c>
@@ -39138,7 +39137,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-226','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF7A-D920-F153-117F010080FD','compareValue','svrBussRepFundInfoDto.sharesType3','==','99','投资企业类型（技术领域）为99其他','E');</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="12" t="s">
         <v>1072</v>
       </c>
@@ -39168,7 +39167,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-221','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E053-007F01006A13','compareValue','svrBussRepFundInfoDto.registOrg1','==','99','[登记备案机构]选择[99 其他]的场合','E');</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="12" t="s">
         <v>1073</v>
       </c>
@@ -39198,7 +39197,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-222','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-F153-107F010077FD','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A192" s="12" t="s">
         <v>1022</v>
       </c>
@@ -39228,7 +39227,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-171','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D161-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','01','当“担保方式”选择“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A193" s="12" t="s">
         <v>1023</v>
       </c>
@@ -39258,7 +39257,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-172','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D162-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','02','当“担保方式”选择“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="12" t="s">
         <v>1078</v>
       </c>
@@ -39288,7 +39287,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-233','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-E050-107F110077FD','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="12" t="s">
         <v>1079</v>
       </c>
@@ -39315,7 +39314,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-234','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL10','inArray','assetType2','==','2607,2610,2611,2612,2613,2617','','E');</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="12" t="s">
         <v>1080</v>
       </c>
@@ -39342,7 +39341,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-235','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL11','inArray','assetType2','==','2610,2611,2612,2613','','E');</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="12" t="s">
         <v>1081</v>
       </c>
@@ -39369,7 +39368,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-236','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL12','inArray','assetType2','==','2610,2611,2612,2613','','E');</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="12" t="s">
         <v>1082</v>
       </c>
@@ -39396,7 +39395,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-237','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL13','inArray','assetType2','==','2610,2611,2612,2613','','E');</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="12" t="s">
         <v>1083</v>
       </c>
@@ -39423,7 +39422,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-238','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL21','inArray','assetType2','==','2101','','E');</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="12" t="s">
         <v>1084</v>
       </c>
@@ -39453,7 +39452,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-239','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL22','inArray','svrBussFinBondRepInfoDto.repRegistOrg','==','99','若“登记托管机构”选择“99 其他”','E');</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="12" t="s">
         <v>1085</v>
       </c>
@@ -39483,7 +39482,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-240','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL23','inArray','svrBussFinBondRepInfoDto.repRegistOrg','!=','99','若“登记托管机构”选择“其他”以外的选项','E');</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A202" s="12" t="s">
         <v>1024</v>
       </c>
@@ -39513,7 +39512,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-173','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D165-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','01','当“担保方式”选择“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="12" t="s">
         <v>2859</v>
       </c>
@@ -39540,7 +39539,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-242','ASSET_INFO_DETAIL_RULE_0000-B66B580F-F249-128E-E053-045AA8C04C6C','inArray','assetType2','==','2601,2602,2604,2605,2606,2607,2610,2611,2612,2613,2614,2616,2617,2618,2619,2620,2699,1106,1303,2401,2402,2403,2499','','E');</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A204" s="12" t="s">
         <v>968</v>
       </c>
@@ -39570,7 +39569,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-116','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000622','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','!=','03,04','“担保方式”不是“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="12" t="s">
         <v>1088</v>
       </c>
@@ -39597,7 +39596,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-244','ASSET_INFO_DETAIL_RULE_0000-B690A5B9-FE54-4725-E053-045AA8C093EE','inArray','assetType2','==','1703,1704,1705,1706,1701,1702','','E');</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="12" t="s">
         <v>1089</v>
       </c>
@@ -39624,7 +39623,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-245','ASSET_INFO_DETAIL_RULE_0000-B690A5B9-FE55-4725-E053-045AA8C093EE','inArray','assetType2','==','1703,1704,1705,1706,1701,1702','','E');</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="12" t="s">
         <v>1090</v>
       </c>
@@ -39654,7 +39653,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-246','ASSET_INFO_DETAIL_RULE_0000-ad57bed1-ad1c-4755-9b27-e73f1e0ebd77','compareValue','svrBussRepEquityInfoDto.sharesType2','==','99','企业类型（按经济类型划分）为“99 其他”','E');</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="12" t="s">
         <v>1091</v>
       </c>
@@ -39681,7 +39680,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-247','ASSET_INFO_DETAIL_RULE_0000-B690A5B9-FE59-4725-E053-045AA8C093EE','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="12" t="s">
         <v>1092</v>
       </c>
@@ -39711,7 +39710,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-249','ASSET_INFO_DETAIL_RULE_0000-952d8ad8-c181-4e7e-b0a2-229183c7af07','compareValue','svrBussRepEquityInfoDto.sharesType3','==','99','企业类型（按技术领域划分）为“99 其他”','E');</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="12" t="s">
         <v>1093</v>
       </c>
@@ -39741,7 +39740,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-250','ASSET_INFO_DETAIL_RULE_0000-e2b0bccf-868d-4d46-aa43-483a2236a1f2','compareValue','svrBussRepEquityInfoDto.sharesType1','==','99','企业类型（按规模划分）为“99 其他”','E');</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="12" t="s">
         <v>1094</v>
       </c>
@@ -39771,7 +39770,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-251','ASSET_INFO_DETAIL_RULE_0000-b9bd2a58-a6cd-4490-b2cc-990b0f767925','compareValue','svrBussFinBondRepInfoDto.repSectype','==','99','具体类别为其他债券时','E');</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="12" t="s">
         <v>1095</v>
       </c>
@@ -39801,7 +39800,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-252','ASSET_INFO_DETAIL_RULE_0000-ad13dd58-bbd2-43c2-a328-6c4b6b88693a','compareValue','svrBussRepEquityInfoDto.sharesType','==','99','股票类型为“99 其他”','E');</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="12" t="s">
         <v>1096</v>
       </c>
@@ -39831,7 +39830,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-253','ASSET_INFO_DETAIL_RULE_0000-1e194cb5-4e03-4115-bdc5-df05520fea4a','compareValue','svrBussFinBondRepInfoDto.repPartyType3','==','99','发行机构类型（按技术领域划分）为“99 其他”','E');</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="12" t="s">
         <v>1097</v>
       </c>
@@ -39861,7 +39860,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-254','ASSET_INFO_DETAIL_RULE_0000-145f8481-b011-4a85-a778-80594045d3ee','compareValue','svrBussFinBondRepInfoDto.repPartyType2','==','99','发行机构类型（按经济类型划分）为“99 其他”','E');</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="12" t="s">
         <v>1098</v>
       </c>
@@ -39891,7 +39890,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-255','ASSET_INFO_DETAIL_RULE_0000-a801d56a-aab3-45a6-8da2-cb4c55452fae','compareValue','svrBussFinBondRepInfoDto.repPartyType1','==','99','发行机构类型（按规模划分）为“99 其他”','E');</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="12" t="s">
         <v>1099</v>
       </c>
@@ -39918,7 +39917,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-256','ASSET_INFO_DETAIL_RULE_0000-59ab0bd6-76fc-4376-a277-fc77e58ebb39','inArray','assetType2','==','1112,1113,1114,1115,1116,1117','','E');</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="12" t="s">
         <v>1100</v>
       </c>
@@ -39945,7 +39944,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-257','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZY28','inArray','assetType2','==','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="12" t="s">
         <v>1101</v>
       </c>
@@ -39972,7 +39971,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-258','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZY27','inArray','assetType2','==','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="12" t="s">
         <v>2105</v>
       </c>
@@ -39999,7 +39998,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-791','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000377','inArray','assetType2','==','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="12" t="s">
         <v>1102</v>
       </c>
@@ -40026,7 +40025,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-259','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZY29','inArray','assetType2','==','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="12" t="s">
         <v>1103</v>
       </c>
@@ -40053,7 +40052,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-266','ASSET_INFO_DETAIL_RULE_0000-6542fcf4-8ef3-445d-be1e-befe58f98787','inArray','assetType2','==','1302,1305','','E');</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="12" t="s">
         <v>1104</v>
       </c>
@@ -40080,7 +40079,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-269','ASSET_INFO_DETAIL_RULE_0000-b46ff785-d69c-4074-8d84-b8f1ccd9a577','inArray','assetType2','==','1301,1302,1305','','E');</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="12" t="s">
         <v>1105</v>
       </c>
@@ -40107,7 +40106,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-270','ASSET_INFO_DETAIL_RULE_0000-9f72f8e8-de6e-4eb4-a70d-0e3ebd7e86f4','inArray','assetType2','==','1301','','E');</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="12" t="s">
         <v>1106</v>
       </c>
@@ -40134,7 +40133,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-271','ASSET_INFO_DETAIL_RULE_0000-d11da57a-1163-4d8e-b5fb-f6f3581189b2','inArray','assetType2','==','1116','','E');</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="12" t="s">
         <v>1107</v>
       </c>
@@ -40161,7 +40160,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-272','ASSET_INFO_DETAIL_RULE_0000-c33b3f9e-2b30-4dbb-8c3d-c4520c3dd4b0','inArray','assetType2','==','1117','','E');</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="12" t="s">
         <v>1108</v>
       </c>
@@ -40188,7 +40187,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-273','ASSET_INFO_DETAIL_RULE_0000-d02bc873-ae7e-4dc7-82f1-7d17027a927d','inArray','assetType2','==','1112','','E');</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="12" t="s">
         <v>1109</v>
       </c>
@@ -40215,7 +40214,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-274','ASSET_INFO_DETAIL_RULE_0000-f08cbfc9-7364-44e1-b9ac-ccc4dc70a2ad','inArray','assetType2','==','1113','','E');</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="12" t="s">
         <v>1110</v>
       </c>
@@ -40242,7 +40241,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-275','ASSET_INFO_DETAIL_RULE_0000-c35975de-3bf7-4b78-9bcd-45e7f9bc227e','inArray','assetType2','==','1115','','E');</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="12" t="s">
         <v>1111</v>
       </c>
@@ -40269,7 +40268,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-276','ASSET_INFO_DETAIL_RULE_0000-cb13d37b-01ac-4078-a7ae-7aea112e6d90','inArray','assetType2','==','1114','','E');</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="12" t="s">
         <v>1112</v>
       </c>
@@ -40296,7 +40295,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-277','ASSET_INFO_DETAIL_RULE_0000-ccea9114-8adc-4341-95ec-a31b93091fda','inArray','assetType2','!=','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="12" t="s">
         <v>1113</v>
       </c>
@@ -40323,7 +40322,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-278','ASSET_INFO_DETAIL_RULE_0000-f032c148-e29d-412e-a829-1ffaf6d70e71','inArray','assetType2','!=','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="12" t="s">
         <v>1114</v>
       </c>
@@ -40350,7 +40349,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-279','ASSET_INFO_DETAIL_RULE_0000-90da2a6d-b448-4486-92bd-c1fdf920684e','inArray','assetType2','!=','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="12" t="s">
         <v>1115</v>
       </c>
@@ -40380,7 +40379,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-281','ASSET_INFO_DETAIL_RULE_0000-979184d8-0972-49df-a57f-bda5e1f6fafc','compareValue','tradeMarket','==','99','当交易流通场所为“99 其他交易流通场所”时','E');</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="12" t="s">
         <v>1116</v>
       </c>
@@ -40407,7 +40406,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-289','ASSET_INFO_DETAIL_RULE_0000-B4D4ACB1-4DA7-14B5-E053-045AA8C0F0EF','inArray','assetType2','==','1301,1302,1305','','E');</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="12" t="s">
         <v>1117</v>
       </c>
@@ -40434,7 +40433,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-290','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-207F01006A53','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="12" t="s">
         <v>1118</v>
       </c>
@@ -40461,7 +40460,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-291','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A55','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="12" t="s">
         <v>1119</v>
       </c>
@@ -40488,7 +40487,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-292','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D161-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="12" t="s">
         <v>1120</v>
       </c>
@@ -40515,7 +40514,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-293','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D162-E050-007F010077FD','inArray','assetType2','==','1299','','E');</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="12" t="s">
         <v>1121</v>
       </c>
@@ -40542,7 +40541,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-294','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D163-E050-007F010077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="12" t="s">
         <v>1122</v>
       </c>
@@ -40569,7 +40568,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-295','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF7A-D920-E051-117F010078FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A241" s="12" t="s">
         <v>1025</v>
       </c>
@@ -40599,7 +40598,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-174','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D166-E050-007F010077FD','compareValue','svrBussRepOtherInvestTargetInfoDto.guaType','==','02','当“担保方式”选择“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="12" t="s">
         <v>1028</v>
       </c>
@@ -40629,7 +40628,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-177','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A52','compareValue','svrBussRepOtherInvestTargetInfoDto.industryFlag','==','02','当项目是否属于重点监控行业和领域为否时','E');</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="12" t="s">
         <v>1029</v>
       </c>
@@ -40659,7 +40658,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-178','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A51','compareValue','svrBussRepOtherInvestTargetInfoDto.industryFlag','==','01','当项目是否属于重点监控行业和领域为是时','E');</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="12" t="s">
         <v>1127</v>
       </c>
@@ -40689,7 +40688,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-300','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-207F01006A53','compareValue','svrBussRepOtherInvestTargetInfoDto.industryFlag','==','02','项目是否属于重点监控行业和领域为否','E');</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="12" t="s">
         <v>1030</v>
       </c>
@@ -40719,7 +40718,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-179','ASSET_INFO_DETAIL_RULE_0000-443E4A49-6810-5A9E-E050-007F01006A53','compareValue','svrBussRepOtherInvestTargetInfoDto.monitType','==','99','当重点监控行业和领域类别为其他时','E');</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="12" t="s">
         <v>1128</v>
       </c>
@@ -40746,7 +40745,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-301','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF71-D920-E050-007F010077FD','inArray','assetType2','==','1301','','E');</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="12" t="s">
         <v>1129</v>
       </c>
@@ -40773,7 +40772,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-302','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D111-E050-007F010077FD','inArray','assetType2','==','1301','','E');</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="12" t="s">
         <v>1130</v>
       </c>
@@ -40800,7 +40799,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-309','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D114-E050-007F010077FD','inArray','assetType2','==','1301,1302,1305','','E');</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="12" t="s">
         <v>1131</v>
       </c>
@@ -40830,7 +40829,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-310','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-E050-107F310077FD','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="12" t="s">
         <v>1132</v>
       </c>
@@ -40860,7 +40859,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-311','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF77-D920-E050-007F110077FD','compareValue','svrBussRepEquityInfoDto.investStage','==','99','投资阶段为99其他','E');</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="12" t="s">
         <v>1133</v>
       </c>
@@ -40887,7 +40886,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-312','ASSET_INFO_DETAIL_RULE_0000-884827E5-DF35-D920-E060-007F010077JX','inArray','assetType2','!=','1112,1113,1114,1115,1116,1117','','E');</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="12" t="s">
         <v>1134</v>
       </c>
@@ -40914,7 +40913,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-313','ASSET_INFO_DETAIL_RULE_0000-884807E5-EF00-D123-E060-007F010077FD','inArray','assetType2','!=','1705,2601,2602,2604,2605,2606,2607,2610,2611,2612,2613,2614,2616,2617,2618,2619,2620,2699','','E');</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A253" s="12" t="s">
         <v>970</v>
       </c>
@@ -40944,7 +40943,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-118','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000662','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','==','03,04','当“担保方式”选择“抵押”或“质押”时','E');</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A254" s="12" t="s">
         <v>971</v>
       </c>
@@ -40974,7 +40973,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-119','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000672','inArray','svrBussRepAssetCreditNonstdInfoDto.repGuaType','==','01,02','当“担保方式”选择“信用担保”或“第三方保证”时','E');</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="12" t="s">
         <v>998</v>
       </c>
@@ -41004,7 +41003,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-147','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000374','compareValue','svrBussRepAssetCreditNonstdInfoDto.repIndustryFlag','==','01','项目是否属于重点监控行业和领域等于01是','E');</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="12" t="s">
         <v>1001</v>
       </c>
@@ -41034,7 +41033,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-150','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000394','compareValue','svrBussRepAssetCreditNonstdInfoDto.repIndustryFlag','==','02','项目是否属于重点监控行业和领域等于02否','E');</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="12" t="s">
         <v>1004</v>
       </c>
@@ -41064,7 +41063,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-153','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000424','compareValue','svrBussRepAssetCreditNonstdInfoDto.repIndustryFlag','==','02','项目是否属于重点监控行业和领域为否','E');</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="12" t="s">
         <v>1002</v>
       </c>
@@ -41094,7 +41093,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-151','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000444','compareValue','svrBussRepAssetCreditNonstdInfoDto.repMonitType','==','99','重点监控行业和领域类别等于99其他','E');</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="12" t="s">
         <v>1141</v>
       </c>
@@ -41121,7 +41120,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-328','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA3-D920-E050-007F010077FD','inArray','assetType2','==','1201,1210','','E');</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="12" t="s">
         <v>1142</v>
       </c>
@@ -41148,7 +41147,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-329','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA3-D920-E050-107F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="12" t="s">
         <v>1143</v>
       </c>
@@ -41175,7 +41174,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-330','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000002','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="12" t="s">
         <v>1144</v>
       </c>
@@ -41202,7 +41201,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-331','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA4-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="12" t="s">
         <v>1145</v>
       </c>
@@ -41229,7 +41228,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-332','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000003','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="12" t="s">
         <v>1146</v>
       </c>
@@ -41256,7 +41255,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-333','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA5-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="12" t="s">
         <v>1147</v>
       </c>
@@ -41283,7 +41282,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-334','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000004','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="12" t="s">
         <v>1148</v>
       </c>
@@ -41310,7 +41309,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-335','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA5-D920-E050-107F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="12" t="s">
         <v>1149</v>
       </c>
@@ -41337,7 +41336,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-336','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000005','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="12" t="s">
         <v>1150</v>
       </c>
@@ -41364,7 +41363,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-337','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA6-D920-E050-007F010077FD','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="12" t="s">
         <v>1151</v>
       </c>
@@ -41391,7 +41390,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-338','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA7-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="12" t="s">
         <v>1152</v>
       </c>
@@ -41418,7 +41417,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-339','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFA8-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="12" t="s">
         <v>1153</v>
       </c>
@@ -41445,7 +41444,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-340','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000006','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="12" t="s">
         <v>1154</v>
       </c>
@@ -41472,7 +41471,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-341','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFAC-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="273" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="12" t="s">
         <v>1155</v>
       </c>
@@ -41499,7 +41498,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-342','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01100009','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="274" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="12" t="s">
         <v>1156</v>
       </c>
@@ -41526,7 +41525,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-343','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB0-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="275" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="12" t="s">
         <v>1157</v>
       </c>
@@ -41553,7 +41552,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-344','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFB4-D920-E050-007F01000010','inArray','assetType2','==','1210','','E');</v>
       </c>
     </row>
-    <row r="276" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="12" t="s">
         <v>1158</v>
       </c>
@@ -41580,7 +41579,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-345','ASSET_INFO_DETAIL_RULE_0000-884807E5-DFAF-D920-E050-007F010077FD','inArray','assetType2','==','1201','','E');</v>
       </c>
     </row>
-    <row r="277" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="12" t="s">
         <v>1159</v>
       </c>
@@ -41607,7 +41606,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-347','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF99-D920-E150-107FX10077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="278" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="12" t="s">
         <v>1160</v>
       </c>
@@ -41634,7 +41633,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-349','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF99-D920-E150-007FX10077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="279" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="12" t="s">
         <v>1161</v>
       </c>
@@ -41661,7 +41660,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-352','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF9B-D922-E150-007F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="280" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="12" t="s">
         <v>1162</v>
       </c>
@@ -41688,7 +41687,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-353','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF9B-D922-E150-107F010077FD','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="281" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="12" t="s">
         <v>1163</v>
       </c>
@@ -41718,7 +41717,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-354','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF8F-D922-E150-007F010077FD','compareValue','svrBussRepOutInvestAgrInfoDto.rateFlag','==','02','是否有预期收益率为否','E');</v>
       </c>
     </row>
-    <row r="282" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="12" t="s">
         <v>1164</v>
       </c>
@@ -41748,7 +41747,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-355','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF8A-D921-E150-007F010077FD','compareValue','svrBussRepOutInvestAgrInfoDto.rateFlag','==','01','是否有预期收益率为是','E');</v>
       </c>
     </row>
-    <row r="283" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="12" t="s">
         <v>1165</v>
       </c>
@@ -41778,7 +41777,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-356','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF8C-D921-E150-007F010077FD','compareValue','svrBussRepOutInvestAgrInfoDto.rateFlag','==','02','是否有预期收益率为否','E');</v>
       </c>
     </row>
-    <row r="284" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="12" t="s">
         <v>1166</v>
       </c>
@@ -41808,7 +41807,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-357','ASSET_INFO_DETAIL_RULE_0000-284807E5-DF28-D920-E060-007F0100ZL27','compareValue','svrBussRepOutInvestAgrInfoDto.proProperty','==','99','委外投资属性选择“99 其他”场合','E');</v>
       </c>
     </row>
-    <row r="285" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="12" t="s">
         <v>1167</v>
       </c>
@@ -41835,7 +41834,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-383','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01000071','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','','E');</v>
       </c>
     </row>
-    <row r="286" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="15" t="s">
         <v>1168</v>
       </c>
@@ -41870,7 +41869,7 @@
       <c r="O286" s="16"/>
       <c r="P286" s="16"/>
     </row>
-    <row r="287" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="15" t="s">
         <v>1169</v>
       </c>
@@ -41905,7 +41904,7 @@
       <c r="O287" s="16"/>
       <c r="P287" s="16"/>
     </row>
-    <row r="288" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="15" t="s">
         <v>1170</v>
       </c>
@@ -41940,7 +41939,7 @@
       <c r="O288" s="16"/>
       <c r="P288" s="16"/>
     </row>
-    <row r="289" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="15" t="s">
         <v>1171</v>
       </c>
@@ -41975,7 +41974,7 @@
       <c r="O289" s="16"/>
       <c r="P289" s="16"/>
     </row>
-    <row r="290" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="15" t="s">
         <v>1172</v>
       </c>
@@ -42010,7 +42009,7 @@
       <c r="O290" s="16"/>
       <c r="P290" s="16"/>
     </row>
-    <row r="291" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="15" t="s">
         <v>1173</v>
       </c>
@@ -42045,7 +42044,7 @@
       <c r="O291" s="16"/>
       <c r="P291" s="16"/>
     </row>
-    <row r="292" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="15" t="s">
         <v>1609</v>
       </c>
@@ -42080,7 +42079,7 @@
       <c r="O292" s="16"/>
       <c r="P292" s="16"/>
     </row>
-    <row r="293" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="12" t="s">
         <v>897</v>
       </c>
@@ -42117,7 +42116,7 @@
       <c r="O293" s="16"/>
       <c r="P293" s="16"/>
     </row>
-    <row r="294" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="15" t="s">
         <v>1175</v>
       </c>
@@ -42152,7 +42151,7 @@
       <c r="O294" s="16"/>
       <c r="P294" s="16"/>
     </row>
-    <row r="295" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="12" t="s">
         <v>898</v>
       </c>
@@ -42189,7 +42188,7 @@
       <c r="O295" s="16"/>
       <c r="P295" s="16"/>
     </row>
-    <row r="296" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="15" t="s">
         <v>1177</v>
       </c>
@@ -42224,7 +42223,7 @@
       <c r="O296" s="16"/>
       <c r="P296" s="16"/>
     </row>
-    <row r="297" spans="1:16" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A297" s="15" t="s">
         <v>2129</v>
       </c>
@@ -42261,7 +42260,7 @@
       <c r="O297" s="16"/>
       <c r="P297" s="16"/>
     </row>
-    <row r="298" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="15" t="s">
         <v>1179</v>
       </c>
@@ -42296,7 +42295,7 @@
       <c r="O298" s="16"/>
       <c r="P298" s="16"/>
     </row>
-    <row r="299" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="15" t="s">
         <v>1180</v>
       </c>
@@ -42331,7 +42330,7 @@
       <c r="O299" s="16"/>
       <c r="P299" s="16"/>
     </row>
-    <row r="300" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="12" t="s">
         <v>1123</v>
       </c>
@@ -42405,7 +42404,7 @@
       <c r="O301" s="16"/>
       <c r="P301" s="16"/>
     </row>
-    <row r="302" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="15" t="s">
         <v>1183</v>
       </c>
@@ -42440,7 +42439,7 @@
       <c r="O302" s="16"/>
       <c r="P302" s="16"/>
     </row>
-    <row r="303" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="15" t="s">
         <v>1184</v>
       </c>
@@ -42475,7 +42474,7 @@
       <c r="O303" s="16"/>
       <c r="P303" s="16"/>
     </row>
-    <row r="304" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="15" t="s">
         <v>1185</v>
       </c>
@@ -42510,7 +42509,7 @@
       <c r="O304" s="16"/>
       <c r="P304" s="16"/>
     </row>
-    <row r="305" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="15" t="s">
         <v>1186</v>
       </c>
@@ -42545,7 +42544,7 @@
       <c r="O305" s="16"/>
       <c r="P305" s="16"/>
     </row>
-    <row r="306" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="15" t="s">
         <v>1187</v>
       </c>
@@ -42580,7 +42579,7 @@
       <c r="O306" s="16"/>
       <c r="P306" s="16"/>
     </row>
-    <row r="307" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="15" t="s">
         <v>1188</v>
       </c>
@@ -42615,7 +42614,7 @@
       <c r="O307" s="16"/>
       <c r="P307" s="16"/>
     </row>
-    <row r="308" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="15" t="s">
         <v>1189</v>
       </c>
@@ -42650,7 +42649,7 @@
       <c r="O308" s="16"/>
       <c r="P308" s="16"/>
     </row>
-    <row r="309" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="15" t="s">
         <v>2083</v>
       </c>
@@ -42685,7 +42684,7 @@
       <c r="O309" s="16"/>
       <c r="P309" s="16"/>
     </row>
-    <row r="310" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="15" t="s">
         <v>1190</v>
       </c>
@@ -42720,7 +42719,7 @@
       <c r="O310" s="16"/>
       <c r="P310" s="16"/>
     </row>
-    <row r="311" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="15" t="s">
         <v>1191</v>
       </c>
@@ -42755,7 +42754,7 @@
       <c r="O311" s="16"/>
       <c r="P311" s="16"/>
     </row>
-    <row r="312" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="12" t="s">
         <v>1027</v>
       </c>
@@ -42792,7 +42791,7 @@
       <c r="O312" s="16"/>
       <c r="P312" s="16"/>
     </row>
-    <row r="313" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="15" t="s">
         <v>1193</v>
       </c>
@@ -42827,7 +42826,7 @@
       <c r="O313" s="16"/>
       <c r="P313" s="16"/>
     </row>
-    <row r="314" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="15" t="s">
         <v>1194</v>
       </c>
@@ -42862,7 +42861,7 @@
       <c r="O314" s="16"/>
       <c r="P314" s="16"/>
     </row>
-    <row r="315" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="15" t="s">
         <v>1195</v>
       </c>
@@ -42897,7 +42896,7 @@
       <c r="O315" s="16"/>
       <c r="P315" s="16"/>
     </row>
-    <row r="316" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="15" t="s">
         <v>1196</v>
       </c>
@@ -42932,7 +42931,7 @@
       <c r="O316" s="16"/>
       <c r="P316" s="16"/>
     </row>
-    <row r="317" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="15" t="s">
         <v>1197</v>
       </c>
@@ -42967,7 +42966,7 @@
       <c r="O317" s="16"/>
       <c r="P317" s="16"/>
     </row>
-    <row r="318" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="15" t="s">
         <v>1198</v>
       </c>
@@ -43002,7 +43001,7 @@
       <c r="O318" s="16"/>
       <c r="P318" s="16"/>
     </row>
-    <row r="319" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="15" t="s">
         <v>1199</v>
       </c>
@@ -43037,7 +43036,7 @@
       <c r="O319" s="16"/>
       <c r="P319" s="16"/>
     </row>
-    <row r="320" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="15" t="s">
         <v>1200</v>
       </c>
@@ -43072,7 +43071,7 @@
       <c r="O320" s="16"/>
       <c r="P320" s="16"/>
     </row>
-    <row r="321" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="15" t="s">
         <v>1201</v>
       </c>
@@ -43107,7 +43106,7 @@
       <c r="O321" s="16"/>
       <c r="P321" s="16"/>
     </row>
-    <row r="322" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="15" t="s">
         <v>1202</v>
       </c>
@@ -43142,7 +43141,7 @@
       <c r="O322" s="16"/>
       <c r="P322" s="16"/>
     </row>
-    <row r="323" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="15" t="s">
         <v>1203</v>
       </c>
@@ -43177,7 +43176,7 @@
       <c r="O323" s="16"/>
       <c r="P323" s="16"/>
     </row>
-    <row r="324" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="15" t="s">
         <v>1204</v>
       </c>
@@ -43212,7 +43211,7 @@
       <c r="O324" s="16"/>
       <c r="P324" s="16"/>
     </row>
-    <row r="325" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="15" t="s">
         <v>2081</v>
       </c>
@@ -43247,7 +43246,7 @@
       <c r="O325" s="16"/>
       <c r="P325" s="16"/>
     </row>
-    <row r="326" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="15" t="s">
         <v>1656</v>
       </c>
@@ -43282,7 +43281,7 @@
       <c r="O326" s="16"/>
       <c r="P326" s="16"/>
     </row>
-    <row r="327" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="15" t="s">
         <v>1657</v>
       </c>
@@ -43317,7 +43316,7 @@
       <c r="O327" s="16"/>
       <c r="P327" s="16"/>
     </row>
-    <row r="328" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="15" t="s">
         <v>1658</v>
       </c>
@@ -43352,7 +43351,7 @@
       <c r="O328" s="16"/>
       <c r="P328" s="16"/>
     </row>
-    <row r="329" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="15" t="s">
         <v>1659</v>
       </c>
@@ -43387,7 +43386,7 @@
       <c r="O329" s="16"/>
       <c r="P329" s="16"/>
     </row>
-    <row r="330" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="15" t="s">
         <v>1660</v>
       </c>
@@ -43422,7 +43421,7 @@
       <c r="O330" s="16"/>
       <c r="P330" s="16"/>
     </row>
-    <row r="331" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="15" t="s">
         <v>1661</v>
       </c>
@@ -43457,7 +43456,7 @@
       <c r="O331" s="16"/>
       <c r="P331" s="16"/>
     </row>
-    <row r="332" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="15" t="s">
         <v>1662</v>
       </c>
@@ -43492,7 +43491,7 @@
       <c r="O332" s="16"/>
       <c r="P332" s="16"/>
     </row>
-    <row r="333" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="15" t="s">
         <v>1663</v>
       </c>
@@ -43527,7 +43526,7 @@
       <c r="O333" s="16"/>
       <c r="P333" s="16"/>
     </row>
-    <row r="334" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="15" t="s">
         <v>1664</v>
       </c>
@@ -43562,7 +43561,7 @@
       <c r="O334" s="16"/>
       <c r="P334" s="16"/>
     </row>
-    <row r="335" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="15" t="s">
         <v>1665</v>
       </c>
@@ -43597,7 +43596,7 @@
       <c r="O335" s="16"/>
       <c r="P335" s="16"/>
     </row>
-    <row r="336" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="15" t="s">
         <v>1666</v>
       </c>
@@ -43632,7 +43631,7 @@
       <c r="O336" s="16"/>
       <c r="P336" s="16"/>
     </row>
-    <row r="337" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="15" t="s">
         <v>1667</v>
       </c>
@@ -43667,7 +43666,7 @@
       <c r="O337" s="16"/>
       <c r="P337" s="16"/>
     </row>
-    <row r="338" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="15" t="s">
         <v>1668</v>
       </c>
@@ -43702,7 +43701,7 @@
       <c r="O338" s="16"/>
       <c r="P338" s="16"/>
     </row>
-    <row r="339" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="15" t="s">
         <v>1669</v>
       </c>
@@ -43737,7 +43736,7 @@
       <c r="O339" s="16"/>
       <c r="P339" s="16"/>
     </row>
-    <row r="340" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="15" t="s">
         <v>1670</v>
       </c>
@@ -43772,7 +43771,7 @@
       <c r="O340" s="16"/>
       <c r="P340" s="16"/>
     </row>
-    <row r="341" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="15" t="s">
         <v>1671</v>
       </c>
@@ -43807,7 +43806,7 @@
       <c r="O341" s="16"/>
       <c r="P341" s="16"/>
     </row>
-    <row r="342" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="15" t="s">
         <v>1672</v>
       </c>
@@ -43842,7 +43841,7 @@
       <c r="O342" s="16"/>
       <c r="P342" s="16"/>
     </row>
-    <row r="343" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="15" t="s">
         <v>1673</v>
       </c>
@@ -43877,7 +43876,7 @@
       <c r="O343" s="16"/>
       <c r="P343" s="16"/>
     </row>
-    <row r="344" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="15" t="s">
         <v>1674</v>
       </c>
@@ -43912,7 +43911,7 @@
       <c r="O344" s="16"/>
       <c r="P344" s="16"/>
     </row>
-    <row r="345" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="15" t="s">
         <v>1675</v>
       </c>
@@ -43947,7 +43946,7 @@
       <c r="O345" s="16"/>
       <c r="P345" s="16"/>
     </row>
-    <row r="346" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="15" t="s">
         <v>1676</v>
       </c>
@@ -43982,7 +43981,7 @@
       <c r="O346" s="16"/>
       <c r="P346" s="16"/>
     </row>
-    <row r="347" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="15" t="s">
         <v>1677</v>
       </c>
@@ -44017,7 +44016,7 @@
       <c r="O347" s="16"/>
       <c r="P347" s="16"/>
     </row>
-    <row r="348" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="15" t="s">
         <v>1678</v>
       </c>
@@ -44052,7 +44051,7 @@
       <c r="O348" s="16"/>
       <c r="P348" s="16"/>
     </row>
-    <row r="349" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="15" t="s">
         <v>1679</v>
       </c>
@@ -44087,7 +44086,7 @@
       <c r="O349" s="16"/>
       <c r="P349" s="16"/>
     </row>
-    <row r="350" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="15" t="s">
         <v>1680</v>
       </c>
@@ -44122,7 +44121,7 @@
       <c r="O350" s="16"/>
       <c r="P350" s="16"/>
     </row>
-    <row r="351" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="15" t="s">
         <v>1681</v>
       </c>
@@ -44157,7 +44156,7 @@
       <c r="O351" s="16"/>
       <c r="P351" s="16"/>
     </row>
-    <row r="352" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="15" t="s">
         <v>1682</v>
       </c>
@@ -44192,7 +44191,7 @@
       <c r="O352" s="16"/>
       <c r="P352" s="16"/>
     </row>
-    <row r="353" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="15" t="s">
         <v>1683</v>
       </c>
@@ -44227,7 +44226,7 @@
       <c r="O353" s="16"/>
       <c r="P353" s="16"/>
     </row>
-    <row r="354" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="15" t="s">
         <v>1684</v>
       </c>
@@ -44262,7 +44261,7 @@
       <c r="O354" s="16"/>
       <c r="P354" s="16"/>
     </row>
-    <row r="355" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="15" t="s">
         <v>1685</v>
       </c>
@@ -44297,7 +44296,7 @@
       <c r="O355" s="16"/>
       <c r="P355" s="16"/>
     </row>
-    <row r="356" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="15" t="s">
         <v>1686</v>
       </c>
@@ -44332,7 +44331,7 @@
       <c r="O356" s="16"/>
       <c r="P356" s="16"/>
     </row>
-    <row r="357" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="15" t="s">
         <v>1687</v>
       </c>
@@ -44367,7 +44366,7 @@
       <c r="O357" s="16"/>
       <c r="P357" s="16"/>
     </row>
-    <row r="358" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="15" t="s">
         <v>1688</v>
       </c>
@@ -44402,7 +44401,7 @@
       <c r="O358" s="16"/>
       <c r="P358" s="16"/>
     </row>
-    <row r="359" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="15" t="s">
         <v>1689</v>
       </c>
@@ -44437,7 +44436,7 @@
       <c r="O359" s="16"/>
       <c r="P359" s="16"/>
     </row>
-    <row r="360" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="15" t="s">
         <v>1690</v>
       </c>
@@ -44472,7 +44471,7 @@
       <c r="O360" s="16"/>
       <c r="P360" s="16"/>
     </row>
-    <row r="361" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="15" t="s">
         <v>1691</v>
       </c>
@@ -44507,7 +44506,7 @@
       <c r="O361" s="16"/>
       <c r="P361" s="16"/>
     </row>
-    <row r="362" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="15" t="s">
         <v>1692</v>
       </c>
@@ -44542,7 +44541,7 @@
       <c r="O362" s="16"/>
       <c r="P362" s="16"/>
     </row>
-    <row r="363" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="15" t="s">
         <v>1693</v>
       </c>
@@ -44577,7 +44576,7 @@
       <c r="O363" s="16"/>
       <c r="P363" s="16"/>
     </row>
-    <row r="364" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="15" t="s">
         <v>1694</v>
       </c>
@@ -44612,7 +44611,7 @@
       <c r="O364" s="16"/>
       <c r="P364" s="16"/>
     </row>
-    <row r="365" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="15" t="s">
         <v>1695</v>
       </c>
@@ -44647,7 +44646,7 @@
       <c r="O365" s="16"/>
       <c r="P365" s="16"/>
     </row>
-    <row r="366" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366" s="15" t="s">
         <v>1696</v>
       </c>
@@ -44682,7 +44681,7 @@
       <c r="O366" s="16"/>
       <c r="P366" s="16"/>
     </row>
-    <row r="367" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367" s="15" t="s">
         <v>1697</v>
       </c>
@@ -44717,7 +44716,7 @@
       <c r="O367" s="16"/>
       <c r="P367" s="16"/>
     </row>
-    <row r="368" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="15" t="s">
         <v>1698</v>
       </c>
@@ -44752,7 +44751,7 @@
       <c r="O368" s="16"/>
       <c r="P368" s="16"/>
     </row>
-    <row r="369" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="15" t="s">
         <v>1699</v>
       </c>
@@ -44787,7 +44786,7 @@
       <c r="O369" s="16"/>
       <c r="P369" s="16"/>
     </row>
-    <row r="370" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="15" t="s">
         <v>1700</v>
       </c>
@@ -44822,7 +44821,7 @@
       <c r="O370" s="16"/>
       <c r="P370" s="16"/>
     </row>
-    <row r="371" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="15" t="s">
         <v>1701</v>
       </c>
@@ -44857,7 +44856,7 @@
       <c r="O371" s="16"/>
       <c r="P371" s="16"/>
     </row>
-    <row r="372" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372" s="15" t="s">
         <v>1702</v>
       </c>
@@ -44892,7 +44891,7 @@
       <c r="O372" s="16"/>
       <c r="P372" s="16"/>
     </row>
-    <row r="373" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="15" t="s">
         <v>1703</v>
       </c>
@@ -44927,7 +44926,7 @@
       <c r="O373" s="16"/>
       <c r="P373" s="16"/>
     </row>
-    <row r="374" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="15" t="s">
         <v>1704</v>
       </c>
@@ -44962,7 +44961,7 @@
       <c r="O374" s="16"/>
       <c r="P374" s="16"/>
     </row>
-    <row r="375" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="15" t="s">
         <v>1705</v>
       </c>
@@ -44997,7 +44996,7 @@
       <c r="O375" s="16"/>
       <c r="P375" s="16"/>
     </row>
-    <row r="376" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="15" t="s">
         <v>1706</v>
       </c>
@@ -45032,7 +45031,7 @@
       <c r="O376" s="16"/>
       <c r="P376" s="16"/>
     </row>
-    <row r="377" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="15" t="s">
         <v>1707</v>
       </c>
@@ -45067,7 +45066,7 @@
       <c r="O377" s="16"/>
       <c r="P377" s="16"/>
     </row>
-    <row r="378" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="15" t="s">
         <v>1708</v>
       </c>
@@ -45102,7 +45101,7 @@
       <c r="O378" s="16"/>
       <c r="P378" s="16"/>
     </row>
-    <row r="379" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="15" t="s">
         <v>1709</v>
       </c>
@@ -45137,7 +45136,7 @@
       <c r="O379" s="16"/>
       <c r="P379" s="16"/>
     </row>
-    <row r="380" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="15" t="s">
         <v>1710</v>
       </c>
@@ -45172,7 +45171,7 @@
       <c r="O380" s="16"/>
       <c r="P380" s="16"/>
     </row>
-    <row r="381" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="15" t="s">
         <v>1711</v>
       </c>
@@ -45207,7 +45206,7 @@
       <c r="O381" s="16"/>
       <c r="P381" s="16"/>
     </row>
-    <row r="382" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="15" t="s">
         <v>1712</v>
       </c>
@@ -45242,7 +45241,7 @@
       <c r="O382" s="16"/>
       <c r="P382" s="16"/>
     </row>
-    <row r="383" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="15" t="s">
         <v>1713</v>
       </c>
@@ -45277,7 +45276,7 @@
       <c r="O383" s="16"/>
       <c r="P383" s="16"/>
     </row>
-    <row r="384" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="15" t="s">
         <v>1714</v>
       </c>
@@ -45312,7 +45311,7 @@
       <c r="O384" s="16"/>
       <c r="P384" s="16"/>
     </row>
-    <row r="385" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="15" t="s">
         <v>1715</v>
       </c>
@@ -45347,7 +45346,7 @@
       <c r="O385" s="16"/>
       <c r="P385" s="16"/>
     </row>
-    <row r="386" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="15" t="s">
         <v>1716</v>
       </c>
@@ -45382,7 +45381,7 @@
       <c r="O386" s="16"/>
       <c r="P386" s="16"/>
     </row>
-    <row r="387" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="15" t="s">
         <v>1717</v>
       </c>
@@ -45417,7 +45416,7 @@
       <c r="O387" s="16"/>
       <c r="P387" s="16"/>
     </row>
-    <row r="388" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="15" t="s">
         <v>1718</v>
       </c>
@@ -45452,7 +45451,7 @@
       <c r="O388" s="16"/>
       <c r="P388" s="16"/>
     </row>
-    <row r="389" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="15" t="s">
         <v>1719</v>
       </c>
@@ -45487,7 +45486,7 @@
       <c r="O389" s="16"/>
       <c r="P389" s="16"/>
     </row>
-    <row r="390" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="15" t="s">
         <v>1720</v>
       </c>
@@ -45522,7 +45521,7 @@
       <c r="O390" s="16"/>
       <c r="P390" s="16"/>
     </row>
-    <row r="391" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="15" t="s">
         <v>1721</v>
       </c>
@@ -45557,7 +45556,7 @@
       <c r="O391" s="16"/>
       <c r="P391" s="16"/>
     </row>
-    <row r="392" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="15" t="s">
         <v>1722</v>
       </c>
@@ -45592,7 +45591,7 @@
       <c r="O392" s="16"/>
       <c r="P392" s="16"/>
     </row>
-    <row r="393" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="15" t="s">
         <v>1723</v>
       </c>
@@ -45627,7 +45626,7 @@
       <c r="O393" s="16"/>
       <c r="P393" s="16"/>
     </row>
-    <row r="394" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="15" t="s">
         <v>1724</v>
       </c>
@@ -45662,7 +45661,7 @@
       <c r="O394" s="16"/>
       <c r="P394" s="16"/>
     </row>
-    <row r="395" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="15" t="s">
         <v>1725</v>
       </c>
@@ -45697,7 +45696,7 @@
       <c r="O395" s="16"/>
       <c r="P395" s="16"/>
     </row>
-    <row r="396" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="15" t="s">
         <v>1726</v>
       </c>
@@ -45732,7 +45731,7 @@
       <c r="O396" s="16"/>
       <c r="P396" s="16"/>
     </row>
-    <row r="397" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="15" t="s">
         <v>1727</v>
       </c>
@@ -45767,7 +45766,7 @@
       <c r="O397" s="16"/>
       <c r="P397" s="16"/>
     </row>
-    <row r="398" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="15" t="s">
         <v>1728</v>
       </c>
@@ -45802,7 +45801,7 @@
       <c r="O398" s="16"/>
       <c r="P398" s="16"/>
     </row>
-    <row r="399" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="15" t="s">
         <v>1729</v>
       </c>
@@ -45837,7 +45836,7 @@
       <c r="O399" s="16"/>
       <c r="P399" s="16"/>
     </row>
-    <row r="400" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="15" t="s">
         <v>1730</v>
       </c>
@@ -45872,7 +45871,7 @@
       <c r="O400" s="16"/>
       <c r="P400" s="16"/>
     </row>
-    <row r="401" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="15" t="s">
         <v>1731</v>
       </c>
@@ -45907,7 +45906,7 @@
       <c r="O401" s="16"/>
       <c r="P401" s="16"/>
     </row>
-    <row r="402" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="15" t="s">
         <v>1732</v>
       </c>
@@ -45942,7 +45941,7 @@
       <c r="O402" s="16"/>
       <c r="P402" s="16"/>
     </row>
-    <row r="403" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="15" t="s">
         <v>1733</v>
       </c>
@@ -45977,7 +45976,7 @@
       <c r="O403" s="16"/>
       <c r="P403" s="16"/>
     </row>
-    <row r="404" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="15" t="s">
         <v>1734</v>
       </c>
@@ -46012,7 +46011,7 @@
       <c r="O404" s="16"/>
       <c r="P404" s="16"/>
     </row>
-    <row r="405" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="15" t="s">
         <v>1735</v>
       </c>
@@ -46047,7 +46046,7 @@
       <c r="O405" s="16"/>
       <c r="P405" s="16"/>
     </row>
-    <row r="406" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="15" t="s">
         <v>1736</v>
       </c>
@@ -46082,7 +46081,7 @@
       <c r="O406" s="16"/>
       <c r="P406" s="16"/>
     </row>
-    <row r="407" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="15" t="s">
         <v>1737</v>
       </c>
@@ -46117,7 +46116,7 @@
       <c r="O407" s="16"/>
       <c r="P407" s="16"/>
     </row>
-    <row r="408" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="15" t="s">
         <v>1738</v>
       </c>
@@ -46152,7 +46151,7 @@
       <c r="O408" s="16"/>
       <c r="P408" s="16"/>
     </row>
-    <row r="409" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="15" t="s">
         <v>1739</v>
       </c>
@@ -46187,7 +46186,7 @@
       <c r="O409" s="16"/>
       <c r="P409" s="16"/>
     </row>
-    <row r="410" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="15" t="s">
         <v>1740</v>
       </c>
@@ -46222,7 +46221,7 @@
       <c r="O410" s="16"/>
       <c r="P410" s="16"/>
     </row>
-    <row r="411" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="15" t="s">
         <v>1741</v>
       </c>
@@ -46257,7 +46256,7 @@
       <c r="O411" s="16"/>
       <c r="P411" s="16"/>
     </row>
-    <row r="412" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="15" t="s">
         <v>1742</v>
       </c>
@@ -46292,7 +46291,7 @@
       <c r="O412" s="16"/>
       <c r="P412" s="16"/>
     </row>
-    <row r="413" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="15" t="s">
         <v>1743</v>
       </c>
@@ -46327,7 +46326,7 @@
       <c r="O413" s="16"/>
       <c r="P413" s="16"/>
     </row>
-    <row r="414" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="15" t="s">
         <v>1744</v>
       </c>
@@ -46362,7 +46361,7 @@
       <c r="O414" s="16"/>
       <c r="P414" s="16"/>
     </row>
-    <row r="415" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="15" t="s">
         <v>1745</v>
       </c>
@@ -46397,7 +46396,7 @@
       <c r="O415" s="16"/>
       <c r="P415" s="16"/>
     </row>
-    <row r="416" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="15" t="s">
         <v>1746</v>
       </c>
@@ -46432,7 +46431,7 @@
       <c r="O416" s="16"/>
       <c r="P416" s="16"/>
     </row>
-    <row r="417" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="15" t="s">
         <v>1747</v>
       </c>
@@ -46467,7 +46466,7 @@
       <c r="O417" s="16"/>
       <c r="P417" s="16"/>
     </row>
-    <row r="418" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="15" t="s">
         <v>1748</v>
       </c>
@@ -46502,7 +46501,7 @@
       <c r="O418" s="16"/>
       <c r="P418" s="16"/>
     </row>
-    <row r="419" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="15" t="s">
         <v>1749</v>
       </c>
@@ -46537,7 +46536,7 @@
       <c r="O419" s="16"/>
       <c r="P419" s="16"/>
     </row>
-    <row r="420" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="15" t="s">
         <v>1750</v>
       </c>
@@ -46572,7 +46571,7 @@
       <c r="O420" s="16"/>
       <c r="P420" s="16"/>
     </row>
-    <row r="421" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="421" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="15" t="s">
         <v>1751</v>
       </c>
@@ -46607,7 +46606,7 @@
       <c r="O421" s="16"/>
       <c r="P421" s="16"/>
     </row>
-    <row r="422" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="422" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="15" t="s">
         <v>1752</v>
       </c>
@@ -46642,7 +46641,7 @@
       <c r="O422" s="16"/>
       <c r="P422" s="16"/>
     </row>
-    <row r="423" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="15" t="s">
         <v>1753</v>
       </c>
@@ -46677,7 +46676,7 @@
       <c r="O423" s="16"/>
       <c r="P423" s="16"/>
     </row>
-    <row r="424" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="15" t="s">
         <v>1754</v>
       </c>
@@ -46712,7 +46711,7 @@
       <c r="O424" s="16"/>
       <c r="P424" s="16"/>
     </row>
-    <row r="425" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="15" t="s">
         <v>1755</v>
       </c>
@@ -46747,7 +46746,7 @@
       <c r="O425" s="16"/>
       <c r="P425" s="16"/>
     </row>
-    <row r="426" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="15" t="s">
         <v>1756</v>
       </c>
@@ -46782,7 +46781,7 @@
       <c r="O426" s="16"/>
       <c r="P426" s="16"/>
     </row>
-    <row r="427" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="15" t="s">
         <v>1757</v>
       </c>
@@ -46817,7 +46816,7 @@
       <c r="O427" s="16"/>
       <c r="P427" s="16"/>
     </row>
-    <row r="428" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="15" t="s">
         <v>1758</v>
       </c>
@@ -46852,7 +46851,7 @@
       <c r="O428" s="16"/>
       <c r="P428" s="16"/>
     </row>
-    <row r="429" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="15" t="s">
         <v>1759</v>
       </c>
@@ -46887,7 +46886,7 @@
       <c r="O429" s="16"/>
       <c r="P429" s="16"/>
     </row>
-    <row r="430" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="15" t="s">
         <v>1760</v>
       </c>
@@ -46922,7 +46921,7 @@
       <c r="O430" s="16"/>
       <c r="P430" s="16"/>
     </row>
-    <row r="431" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="15" t="s">
         <v>1761</v>
       </c>
@@ -46957,7 +46956,7 @@
       <c r="O431" s="16"/>
       <c r="P431" s="16"/>
     </row>
-    <row r="432" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="432" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="15" t="s">
         <v>1762</v>
       </c>
@@ -46992,7 +46991,7 @@
       <c r="O432" s="16"/>
       <c r="P432" s="16"/>
     </row>
-    <row r="433" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="15" t="s">
         <v>1763</v>
       </c>
@@ -47027,7 +47026,7 @@
       <c r="O433" s="16"/>
       <c r="P433" s="16"/>
     </row>
-    <row r="434" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="15" t="s">
         <v>1764</v>
       </c>
@@ -47062,7 +47061,7 @@
       <c r="O434" s="16"/>
       <c r="P434" s="16"/>
     </row>
-    <row r="435" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="15" t="s">
         <v>1765</v>
       </c>
@@ -47097,7 +47096,7 @@
       <c r="O435" s="16"/>
       <c r="P435" s="16"/>
     </row>
-    <row r="436" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="15" t="s">
         <v>1766</v>
       </c>
@@ -47132,7 +47131,7 @@
       <c r="O436" s="16"/>
       <c r="P436" s="16"/>
     </row>
-    <row r="437" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="437" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="15" t="s">
         <v>1767</v>
       </c>
@@ -47167,7 +47166,7 @@
       <c r="O437" s="16"/>
       <c r="P437" s="16"/>
     </row>
-    <row r="438" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="15" t="s">
         <v>1768</v>
       </c>
@@ -47202,7 +47201,7 @@
       <c r="O438" s="16"/>
       <c r="P438" s="16"/>
     </row>
-    <row r="439" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="15" t="s">
         <v>1769</v>
       </c>
@@ -47237,7 +47236,7 @@
       <c r="O439" s="16"/>
       <c r="P439" s="16"/>
     </row>
-    <row r="440" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="440" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="15" t="s">
         <v>1770</v>
       </c>
@@ -47272,7 +47271,7 @@
       <c r="O440" s="16"/>
       <c r="P440" s="16"/>
     </row>
-    <row r="441" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="441" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="15" t="s">
         <v>1771</v>
       </c>
@@ -47307,7 +47306,7 @@
       <c r="O441" s="16"/>
       <c r="P441" s="16"/>
     </row>
-    <row r="442" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="442" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="15" t="s">
         <v>1772</v>
       </c>
@@ -47342,7 +47341,7 @@
       <c r="O442" s="16"/>
       <c r="P442" s="16"/>
     </row>
-    <row r="443" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="15" t="s">
         <v>1773</v>
       </c>
@@ -47377,7 +47376,7 @@
       <c r="O443" s="16"/>
       <c r="P443" s="16"/>
     </row>
-    <row r="444" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444" s="15" t="s">
         <v>1774</v>
       </c>
@@ -47412,7 +47411,7 @@
       <c r="O444" s="16"/>
       <c r="P444" s="16"/>
     </row>
-    <row r="445" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="445" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445" s="15" t="s">
         <v>1775</v>
       </c>
@@ -47447,7 +47446,7 @@
       <c r="O445" s="16"/>
       <c r="P445" s="16"/>
     </row>
-    <row r="446" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="446" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446" s="15" t="s">
         <v>1776</v>
       </c>
@@ -47482,7 +47481,7 @@
       <c r="O446" s="16"/>
       <c r="P446" s="16"/>
     </row>
-    <row r="447" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="447" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447" s="15" t="s">
         <v>1777</v>
       </c>
@@ -47517,7 +47516,7 @@
       <c r="O447" s="16"/>
       <c r="P447" s="16"/>
     </row>
-    <row r="448" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="448" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448" s="15" t="s">
         <v>1778</v>
       </c>
@@ -47552,7 +47551,7 @@
       <c r="O448" s="16"/>
       <c r="P448" s="16"/>
     </row>
-    <row r="449" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="449" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449" s="15" t="s">
         <v>1779</v>
       </c>
@@ -47587,7 +47586,7 @@
       <c r="O449" s="16"/>
       <c r="P449" s="16"/>
     </row>
-    <row r="450" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="450" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450" s="15" t="s">
         <v>1780</v>
       </c>
@@ -47622,7 +47621,7 @@
       <c r="O450" s="16"/>
       <c r="P450" s="16"/>
     </row>
-    <row r="451" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="451" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451" s="15" t="s">
         <v>1781</v>
       </c>
@@ -47657,7 +47656,7 @@
       <c r="O451" s="16"/>
       <c r="P451" s="16"/>
     </row>
-    <row r="452" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="452" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="15" t="s">
         <v>1782</v>
       </c>
@@ -47692,7 +47691,7 @@
       <c r="O452" s="16"/>
       <c r="P452" s="16"/>
     </row>
-    <row r="453" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="453" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453" s="15" t="s">
         <v>1783</v>
       </c>
@@ -47727,7 +47726,7 @@
       <c r="O453" s="16"/>
       <c r="P453" s="16"/>
     </row>
-    <row r="454" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="454" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454" s="15" t="s">
         <v>1784</v>
       </c>
@@ -47762,7 +47761,7 @@
       <c r="O454" s="16"/>
       <c r="P454" s="16"/>
     </row>
-    <row r="455" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="455" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455" s="15" t="s">
         <v>1785</v>
       </c>
@@ -47797,7 +47796,7 @@
       <c r="O455" s="16"/>
       <c r="P455" s="16"/>
     </row>
-    <row r="456" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="456" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456" s="15" t="s">
         <v>1786</v>
       </c>
@@ -47832,7 +47831,7 @@
       <c r="O456" s="16"/>
       <c r="P456" s="16"/>
     </row>
-    <row r="457" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="457" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457" s="15" t="s">
         <v>1787</v>
       </c>
@@ -47867,7 +47866,7 @@
       <c r="O457" s="16"/>
       <c r="P457" s="16"/>
     </row>
-    <row r="458" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="458" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A458" s="15" t="s">
         <v>1788</v>
       </c>
@@ -47902,7 +47901,7 @@
       <c r="O458" s="16"/>
       <c r="P458" s="16"/>
     </row>
-    <row r="459" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="459" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459" s="15" t="s">
         <v>1789</v>
       </c>
@@ -47937,7 +47936,7 @@
       <c r="O459" s="16"/>
       <c r="P459" s="16"/>
     </row>
-    <row r="460" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="460" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A460" s="15" t="s">
         <v>1790</v>
       </c>
@@ -47972,7 +47971,7 @@
       <c r="O460" s="16"/>
       <c r="P460" s="16"/>
     </row>
-    <row r="461" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="461" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461" s="15" t="s">
         <v>1791</v>
       </c>
@@ -48007,7 +48006,7 @@
       <c r="O461" s="16"/>
       <c r="P461" s="16"/>
     </row>
-    <row r="462" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="462" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462" s="15" t="s">
         <v>1792</v>
       </c>
@@ -48042,7 +48041,7 @@
       <c r="O462" s="16"/>
       <c r="P462" s="16"/>
     </row>
-    <row r="463" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="463" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463" s="15" t="s">
         <v>1793</v>
       </c>
@@ -48077,7 +48076,7 @@
       <c r="O463" s="16"/>
       <c r="P463" s="16"/>
     </row>
-    <row r="464" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="464" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A464" s="15" t="s">
         <v>1794</v>
       </c>
@@ -48112,7 +48111,7 @@
       <c r="O464" s="16"/>
       <c r="P464" s="16"/>
     </row>
-    <row r="465" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="465" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="15" t="s">
         <v>1795</v>
       </c>
@@ -48147,7 +48146,7 @@
       <c r="O465" s="16"/>
       <c r="P465" s="16"/>
     </row>
-    <row r="466" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="15" t="s">
         <v>1796</v>
       </c>
@@ -48182,7 +48181,7 @@
       <c r="O466" s="16"/>
       <c r="P466" s="16"/>
     </row>
-    <row r="467" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="467" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="15" t="s">
         <v>1797</v>
       </c>
@@ -48217,7 +48216,7 @@
       <c r="O467" s="16"/>
       <c r="P467" s="16"/>
     </row>
-    <row r="468" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="468" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="15" t="s">
         <v>1798</v>
       </c>
@@ -48252,7 +48251,7 @@
       <c r="O468" s="16"/>
       <c r="P468" s="16"/>
     </row>
-    <row r="469" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="469" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469" s="15" t="s">
         <v>1799</v>
       </c>
@@ -48287,7 +48286,7 @@
       <c r="O469" s="16"/>
       <c r="P469" s="16"/>
     </row>
-    <row r="470" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="470" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="15" t="s">
         <v>1800</v>
       </c>
@@ -48322,7 +48321,7 @@
       <c r="O470" s="16"/>
       <c r="P470" s="16"/>
     </row>
-    <row r="471" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="471" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="15" t="s">
         <v>1801</v>
       </c>
@@ -48357,7 +48356,7 @@
       <c r="O471" s="16"/>
       <c r="P471" s="16"/>
     </row>
-    <row r="472" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="472" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="15" t="s">
         <v>1802</v>
       </c>
@@ -48392,7 +48391,7 @@
       <c r="O472" s="16"/>
       <c r="P472" s="16"/>
     </row>
-    <row r="473" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="473" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="15" t="s">
         <v>1803</v>
       </c>
@@ -48427,7 +48426,7 @@
       <c r="O473" s="16"/>
       <c r="P473" s="16"/>
     </row>
-    <row r="474" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="474" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="15" t="s">
         <v>1804</v>
       </c>
@@ -48462,7 +48461,7 @@
       <c r="O474" s="16"/>
       <c r="P474" s="16"/>
     </row>
-    <row r="475" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="475" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="15" t="s">
         <v>1805</v>
       </c>
@@ -48497,7 +48496,7 @@
       <c r="O475" s="16"/>
       <c r="P475" s="16"/>
     </row>
-    <row r="476" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="476" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="15" t="s">
         <v>1806</v>
       </c>
@@ -48532,7 +48531,7 @@
       <c r="O476" s="16"/>
       <c r="P476" s="16"/>
     </row>
-    <row r="477" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="477" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477" s="15" t="s">
         <v>1807</v>
       </c>
@@ -48567,7 +48566,7 @@
       <c r="O477" s="16"/>
       <c r="P477" s="16"/>
     </row>
-    <row r="478" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="478" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A478" s="15" t="s">
         <v>1808</v>
       </c>
@@ -48602,7 +48601,7 @@
       <c r="O478" s="16"/>
       <c r="P478" s="16"/>
     </row>
-    <row r="479" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="479" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A479" s="15" t="s">
         <v>1809</v>
       </c>
@@ -48637,7 +48636,7 @@
       <c r="O479" s="16"/>
       <c r="P479" s="16"/>
     </row>
-    <row r="480" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="480" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="15" t="s">
         <v>1810</v>
       </c>
@@ -48672,7 +48671,7 @@
       <c r="O480" s="16"/>
       <c r="P480" s="16"/>
     </row>
-    <row r="481" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="481" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481" s="15" t="s">
         <v>1811</v>
       </c>
@@ -48707,7 +48706,7 @@
       <c r="O481" s="16"/>
       <c r="P481" s="16"/>
     </row>
-    <row r="482" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="482" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A482" s="15" t="s">
         <v>1812</v>
       </c>
@@ -48742,7 +48741,7 @@
       <c r="O482" s="16"/>
       <c r="P482" s="16"/>
     </row>
-    <row r="483" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="483" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A483" s="15" t="s">
         <v>1813</v>
       </c>
@@ -48777,7 +48776,7 @@
       <c r="O483" s="16"/>
       <c r="P483" s="16"/>
     </row>
-    <row r="484" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="484" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A484" s="15" t="s">
         <v>1814</v>
       </c>
@@ -48812,7 +48811,7 @@
       <c r="O484" s="16"/>
       <c r="P484" s="16"/>
     </row>
-    <row r="485" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="485" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A485" s="15" t="s">
         <v>1815</v>
       </c>
@@ -48847,7 +48846,7 @@
       <c r="O485" s="16"/>
       <c r="P485" s="16"/>
     </row>
-    <row r="486" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="486" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A486" s="15" t="s">
         <v>1816</v>
       </c>
@@ -48882,7 +48881,7 @@
       <c r="O486" s="16"/>
       <c r="P486" s="16"/>
     </row>
-    <row r="487" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="487" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A487" s="15" t="s">
         <v>1817</v>
       </c>
@@ -48917,7 +48916,7 @@
       <c r="O487" s="16"/>
       <c r="P487" s="16"/>
     </row>
-    <row r="488" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="488" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A488" s="15" t="s">
         <v>1818</v>
       </c>
@@ -48952,7 +48951,7 @@
       <c r="O488" s="16"/>
       <c r="P488" s="16"/>
     </row>
-    <row r="489" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="489" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A489" s="15" t="s">
         <v>1819</v>
       </c>
@@ -48987,7 +48986,7 @@
       <c r="O489" s="16"/>
       <c r="P489" s="16"/>
     </row>
-    <row r="490" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="490" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A490" s="15" t="s">
         <v>1820</v>
       </c>
@@ -49022,7 +49021,7 @@
       <c r="O490" s="16"/>
       <c r="P490" s="16"/>
     </row>
-    <row r="491" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="491" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A491" s="15" t="s">
         <v>1821</v>
       </c>
@@ -49057,7 +49056,7 @@
       <c r="O491" s="16"/>
       <c r="P491" s="16"/>
     </row>
-    <row r="492" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="492" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A492" s="15" t="s">
         <v>1822</v>
       </c>
@@ -49092,7 +49091,7 @@
       <c r="O492" s="16"/>
       <c r="P492" s="16"/>
     </row>
-    <row r="493" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="493" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A493" s="15" t="s">
         <v>1823</v>
       </c>
@@ -49127,7 +49126,7 @@
       <c r="O493" s="16"/>
       <c r="P493" s="16"/>
     </row>
-    <row r="494" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="494" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A494" s="15" t="s">
         <v>1824</v>
       </c>
@@ -49162,7 +49161,7 @@
       <c r="O494" s="16"/>
       <c r="P494" s="16"/>
     </row>
-    <row r="495" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="495" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A495" s="15" t="s">
         <v>1825</v>
       </c>
@@ -49197,7 +49196,7 @@
       <c r="O495" s="16"/>
       <c r="P495" s="16"/>
     </row>
-    <row r="496" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="496" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A496" s="15" t="s">
         <v>1826</v>
       </c>
@@ -49232,7 +49231,7 @@
       <c r="O496" s="16"/>
       <c r="P496" s="16"/>
     </row>
-    <row r="497" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="497" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A497" s="15" t="s">
         <v>1827</v>
       </c>
@@ -49267,7 +49266,7 @@
       <c r="O497" s="16"/>
       <c r="P497" s="16"/>
     </row>
-    <row r="498" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="498" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A498" s="15" t="s">
         <v>1828</v>
       </c>
@@ -49302,7 +49301,7 @@
       <c r="O498" s="16"/>
       <c r="P498" s="16"/>
     </row>
-    <row r="499" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="499" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A499" s="15" t="s">
         <v>1829</v>
       </c>
@@ -49337,7 +49336,7 @@
       <c r="O499" s="16"/>
       <c r="P499" s="16"/>
     </row>
-    <row r="500" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="500" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A500" s="15" t="s">
         <v>1830</v>
       </c>
@@ -49372,7 +49371,7 @@
       <c r="O500" s="16"/>
       <c r="P500" s="16"/>
     </row>
-    <row r="501" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="501" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A501" s="15" t="s">
         <v>1831</v>
       </c>
@@ -49407,7 +49406,7 @@
       <c r="O501" s="16"/>
       <c r="P501" s="16"/>
     </row>
-    <row r="502" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="502" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A502" s="15" t="s">
         <v>1832</v>
       </c>
@@ -49442,7 +49441,7 @@
       <c r="O502" s="16"/>
       <c r="P502" s="16"/>
     </row>
-    <row r="503" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="503" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A503" s="15" t="s">
         <v>1833</v>
       </c>
@@ -49477,7 +49476,7 @@
       <c r="O503" s="16"/>
       <c r="P503" s="16"/>
     </row>
-    <row r="504" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="504" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A504" s="15" t="s">
         <v>1834</v>
       </c>
@@ -49512,7 +49511,7 @@
       <c r="O504" s="16"/>
       <c r="P504" s="16"/>
     </row>
-    <row r="505" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="505" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A505" s="15" t="s">
         <v>1835</v>
       </c>
@@ -49547,7 +49546,7 @@
       <c r="O505" s="16"/>
       <c r="P505" s="16"/>
     </row>
-    <row r="506" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="506" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A506" s="15" t="s">
         <v>1836</v>
       </c>
@@ -49582,7 +49581,7 @@
       <c r="O506" s="16"/>
       <c r="P506" s="16"/>
     </row>
-    <row r="507" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="507" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A507" s="15" t="s">
         <v>1837</v>
       </c>
@@ -49617,7 +49616,7 @@
       <c r="O507" s="16"/>
       <c r="P507" s="16"/>
     </row>
-    <row r="508" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="508" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A508" s="15" t="s">
         <v>1838</v>
       </c>
@@ -49652,7 +49651,7 @@
       <c r="O508" s="16"/>
       <c r="P508" s="16"/>
     </row>
-    <row r="509" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="509" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A509" s="15" t="s">
         <v>1839</v>
       </c>
@@ -49687,7 +49686,7 @@
       <c r="O509" s="16"/>
       <c r="P509" s="16"/>
     </row>
-    <row r="510" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="510" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A510" s="15" t="s">
         <v>1840</v>
       </c>
@@ -49722,7 +49721,7 @@
       <c r="O510" s="16"/>
       <c r="P510" s="16"/>
     </row>
-    <row r="511" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="511" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A511" s="15" t="s">
         <v>1841</v>
       </c>
@@ -49757,7 +49756,7 @@
       <c r="O511" s="16"/>
       <c r="P511" s="16"/>
     </row>
-    <row r="512" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="512" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A512" s="15" t="s">
         <v>1842</v>
       </c>
@@ -49792,7 +49791,7 @@
       <c r="O512" s="16"/>
       <c r="P512" s="16"/>
     </row>
-    <row r="513" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="513" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A513" s="15" t="s">
         <v>1843</v>
       </c>
@@ -49827,7 +49826,7 @@
       <c r="O513" s="16"/>
       <c r="P513" s="16"/>
     </row>
-    <row r="514" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="514" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A514" s="15" t="s">
         <v>1844</v>
       </c>
@@ -49862,7 +49861,7 @@
       <c r="O514" s="16"/>
       <c r="P514" s="16"/>
     </row>
-    <row r="515" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="515" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A515" s="15" t="s">
         <v>1845</v>
       </c>
@@ -49897,7 +49896,7 @@
       <c r="O515" s="16"/>
       <c r="P515" s="16"/>
     </row>
-    <row r="516" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="516" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A516" s="15" t="s">
         <v>1846</v>
       </c>
@@ -49932,7 +49931,7 @@
       <c r="O516" s="16"/>
       <c r="P516" s="16"/>
     </row>
-    <row r="517" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="517" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A517" s="15" t="s">
         <v>1847</v>
       </c>
@@ -49967,7 +49966,7 @@
       <c r="O517" s="16"/>
       <c r="P517" s="16"/>
     </row>
-    <row r="518" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="518" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A518" s="15" t="s">
         <v>1848</v>
       </c>
@@ -50002,7 +50001,7 @@
       <c r="O518" s="16"/>
       <c r="P518" s="16"/>
     </row>
-    <row r="519" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="519" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A519" s="15" t="s">
         <v>1849</v>
       </c>
@@ -50037,7 +50036,7 @@
       <c r="O519" s="16"/>
       <c r="P519" s="16"/>
     </row>
-    <row r="520" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="520" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A520" s="15" t="s">
         <v>1850</v>
       </c>
@@ -50072,7 +50071,7 @@
       <c r="O520" s="16"/>
       <c r="P520" s="16"/>
     </row>
-    <row r="521" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="521" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A521" s="15" t="s">
         <v>1851</v>
       </c>
@@ -50107,7 +50106,7 @@
       <c r="O521" s="16"/>
       <c r="P521" s="16"/>
     </row>
-    <row r="522" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="522" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A522" s="15" t="s">
         <v>1852</v>
       </c>
@@ -50142,7 +50141,7 @@
       <c r="O522" s="16"/>
       <c r="P522" s="16"/>
     </row>
-    <row r="523" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="523" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A523" s="15" t="s">
         <v>1853</v>
       </c>
@@ -50177,7 +50176,7 @@
       <c r="O523" s="16"/>
       <c r="P523" s="16"/>
     </row>
-    <row r="524" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="524" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A524" s="15" t="s">
         <v>1854</v>
       </c>
@@ -50212,7 +50211,7 @@
       <c r="O524" s="16"/>
       <c r="P524" s="16"/>
     </row>
-    <row r="525" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="525" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A525" s="15" t="s">
         <v>1855</v>
       </c>
@@ -50247,7 +50246,7 @@
       <c r="O525" s="16"/>
       <c r="P525" s="16"/>
     </row>
-    <row r="526" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="526" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A526" s="15" t="s">
         <v>1856</v>
       </c>
@@ -50282,7 +50281,7 @@
       <c r="O526" s="16"/>
       <c r="P526" s="16"/>
     </row>
-    <row r="527" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="527" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A527" s="15" t="s">
         <v>1857</v>
       </c>
@@ -50317,7 +50316,7 @@
       <c r="O527" s="16"/>
       <c r="P527" s="16"/>
     </row>
-    <row r="528" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="528" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A528" s="15" t="s">
         <v>1858</v>
       </c>
@@ -50352,7 +50351,7 @@
       <c r="O528" s="16"/>
       <c r="P528" s="16"/>
     </row>
-    <row r="529" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="529" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A529" s="15" t="s">
         <v>1859</v>
       </c>
@@ -50387,7 +50386,7 @@
       <c r="O529" s="16"/>
       <c r="P529" s="16"/>
     </row>
-    <row r="530" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="530" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A530" s="15" t="s">
         <v>1860</v>
       </c>
@@ -50422,7 +50421,7 @@
       <c r="O530" s="16"/>
       <c r="P530" s="16"/>
     </row>
-    <row r="531" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="531" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A531" s="15" t="s">
         <v>1861</v>
       </c>
@@ -50457,7 +50456,7 @@
       <c r="O531" s="16"/>
       <c r="P531" s="16"/>
     </row>
-    <row r="532" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="532" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A532" s="15" t="s">
         <v>1862</v>
       </c>
@@ -50492,7 +50491,7 @@
       <c r="O532" s="16"/>
       <c r="P532" s="16"/>
     </row>
-    <row r="533" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="533" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A533" s="15" t="s">
         <v>1863</v>
       </c>
@@ -50527,7 +50526,7 @@
       <c r="O533" s="16"/>
       <c r="P533" s="16"/>
     </row>
-    <row r="534" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="534" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A534" s="15" t="s">
         <v>1864</v>
       </c>
@@ -50562,7 +50561,7 @@
       <c r="O534" s="16"/>
       <c r="P534" s="16"/>
     </row>
-    <row r="535" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="535" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A535" s="15" t="s">
         <v>1865</v>
       </c>
@@ -50597,7 +50596,7 @@
       <c r="O535" s="16"/>
       <c r="P535" s="16"/>
     </row>
-    <row r="536" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="536" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A536" s="15" t="s">
         <v>1866</v>
       </c>
@@ -50632,7 +50631,7 @@
       <c r="O536" s="16"/>
       <c r="P536" s="16"/>
     </row>
-    <row r="537" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="537" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A537" s="15" t="s">
         <v>1867</v>
       </c>
@@ -50667,7 +50666,7 @@
       <c r="O537" s="16"/>
       <c r="P537" s="16"/>
     </row>
-    <row r="538" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="538" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A538" s="15" t="s">
         <v>1868</v>
       </c>
@@ -50702,7 +50701,7 @@
       <c r="O538" s="16"/>
       <c r="P538" s="16"/>
     </row>
-    <row r="539" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="539" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A539" s="15" t="s">
         <v>1869</v>
       </c>
@@ -50737,7 +50736,7 @@
       <c r="O539" s="16"/>
       <c r="P539" s="16"/>
     </row>
-    <row r="540" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="540" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A540" s="15" t="s">
         <v>1870</v>
       </c>
@@ -50772,7 +50771,7 @@
       <c r="O540" s="16"/>
       <c r="P540" s="16"/>
     </row>
-    <row r="541" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="541" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A541" s="15" t="s">
         <v>1871</v>
       </c>
@@ -50807,7 +50806,7 @@
       <c r="O541" s="16"/>
       <c r="P541" s="16"/>
     </row>
-    <row r="542" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="542" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A542" s="15" t="s">
         <v>1872</v>
       </c>
@@ -50842,7 +50841,7 @@
       <c r="O542" s="16"/>
       <c r="P542" s="16"/>
     </row>
-    <row r="543" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="543" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A543" s="15" t="s">
         <v>1873</v>
       </c>
@@ -50877,7 +50876,7 @@
       <c r="O543" s="16"/>
       <c r="P543" s="16"/>
     </row>
-    <row r="544" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="544" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A544" s="15" t="s">
         <v>1874</v>
       </c>
@@ -50912,7 +50911,7 @@
       <c r="O544" s="16"/>
       <c r="P544" s="16"/>
     </row>
-    <row r="545" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="545" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A545" s="15" t="s">
         <v>1875</v>
       </c>
@@ -50947,7 +50946,7 @@
       <c r="O545" s="16"/>
       <c r="P545" s="16"/>
     </row>
-    <row r="546" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="546" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A546" s="15" t="s">
         <v>1876</v>
       </c>
@@ -50982,7 +50981,7 @@
       <c r="O546" s="16"/>
       <c r="P546" s="16"/>
     </row>
-    <row r="547" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="547" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A547" s="15" t="s">
         <v>1877</v>
       </c>
@@ -51017,7 +51016,7 @@
       <c r="O547" s="16"/>
       <c r="P547" s="16"/>
     </row>
-    <row r="548" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="548" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A548" s="15" t="s">
         <v>1878</v>
       </c>
@@ -51052,7 +51051,7 @@
       <c r="O548" s="16"/>
       <c r="P548" s="16"/>
     </row>
-    <row r="549" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="549" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A549" s="15" t="s">
         <v>1879</v>
       </c>
@@ -51087,7 +51086,7 @@
       <c r="O549" s="16"/>
       <c r="P549" s="16"/>
     </row>
-    <row r="550" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="550" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A550" s="15" t="s">
         <v>1880</v>
       </c>
@@ -51122,7 +51121,7 @@
       <c r="O550" s="16"/>
       <c r="P550" s="16"/>
     </row>
-    <row r="551" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="551" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A551" s="15" t="s">
         <v>1881</v>
       </c>
@@ -51157,7 +51156,7 @@
       <c r="O551" s="16"/>
       <c r="P551" s="16"/>
     </row>
-    <row r="552" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="552" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A552" s="15" t="s">
         <v>1882</v>
       </c>
@@ -51192,7 +51191,7 @@
       <c r="O552" s="16"/>
       <c r="P552" s="16"/>
     </row>
-    <row r="553" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="553" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A553" s="15" t="s">
         <v>1883</v>
       </c>
@@ -51227,7 +51226,7 @@
       <c r="O553" s="16"/>
       <c r="P553" s="16"/>
     </row>
-    <row r="554" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="554" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A554" s="15" t="s">
         <v>1884</v>
       </c>
@@ -51262,7 +51261,7 @@
       <c r="O554" s="16"/>
       <c r="P554" s="16"/>
     </row>
-    <row r="555" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="555" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A555" s="15" t="s">
         <v>1885</v>
       </c>
@@ -51297,7 +51296,7 @@
       <c r="O555" s="16"/>
       <c r="P555" s="16"/>
     </row>
-    <row r="556" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="556" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A556" s="15" t="s">
         <v>1886</v>
       </c>
@@ -51332,7 +51331,7 @@
       <c r="O556" s="16"/>
       <c r="P556" s="16"/>
     </row>
-    <row r="557" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="557" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A557" s="15" t="s">
         <v>1887</v>
       </c>
@@ -51367,7 +51366,7 @@
       <c r="O557" s="16"/>
       <c r="P557" s="16"/>
     </row>
-    <row r="558" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="558" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A558" s="15" t="s">
         <v>1888</v>
       </c>
@@ -51402,7 +51401,7 @@
       <c r="O558" s="16"/>
       <c r="P558" s="16"/>
     </row>
-    <row r="559" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="559" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A559" s="15" t="s">
         <v>1889</v>
       </c>
@@ -51437,7 +51436,7 @@
       <c r="O559" s="16"/>
       <c r="P559" s="16"/>
     </row>
-    <row r="560" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="560" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A560" s="15" t="s">
         <v>1890</v>
       </c>
@@ -51472,7 +51471,7 @@
       <c r="O560" s="16"/>
       <c r="P560" s="16"/>
     </row>
-    <row r="561" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="561" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A561" s="15" t="s">
         <v>1891</v>
       </c>
@@ -51507,7 +51506,7 @@
       <c r="O561" s="16"/>
       <c r="P561" s="16"/>
     </row>
-    <row r="562" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="562" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A562" s="15" t="s">
         <v>1892</v>
       </c>
@@ -51542,7 +51541,7 @@
       <c r="O562" s="16"/>
       <c r="P562" s="16"/>
     </row>
-    <row r="563" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="563" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A563" s="15" t="s">
         <v>1893</v>
       </c>
@@ -51577,7 +51576,7 @@
       <c r="O563" s="16"/>
       <c r="P563" s="16"/>
     </row>
-    <row r="564" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="564" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A564" s="15" t="s">
         <v>1894</v>
       </c>
@@ -51612,7 +51611,7 @@
       <c r="O564" s="16"/>
       <c r="P564" s="16"/>
     </row>
-    <row r="565" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="565" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A565" s="15" t="s">
         <v>1895</v>
       </c>
@@ -51647,7 +51646,7 @@
       <c r="O565" s="16"/>
       <c r="P565" s="16"/>
     </row>
-    <row r="566" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="566" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A566" s="15" t="s">
         <v>1896</v>
       </c>
@@ -51682,7 +51681,7 @@
       <c r="O566" s="16"/>
       <c r="P566" s="16"/>
     </row>
-    <row r="567" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="567" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A567" s="15" t="s">
         <v>1897</v>
       </c>
@@ -51717,7 +51716,7 @@
       <c r="O567" s="16"/>
       <c r="P567" s="16"/>
     </row>
-    <row r="568" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="568" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A568" s="15" t="s">
         <v>1898</v>
       </c>
@@ -51752,7 +51751,7 @@
       <c r="O568" s="16"/>
       <c r="P568" s="16"/>
     </row>
-    <row r="569" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="569" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A569" s="15" t="s">
         <v>1899</v>
       </c>
@@ -51787,7 +51786,7 @@
       <c r="O569" s="16"/>
       <c r="P569" s="16"/>
     </row>
-    <row r="570" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="570" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A570" s="15" t="s">
         <v>1900</v>
       </c>
@@ -51822,7 +51821,7 @@
       <c r="O570" s="16"/>
       <c r="P570" s="16"/>
     </row>
-    <row r="571" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="571" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A571" s="15" t="s">
         <v>1901</v>
       </c>
@@ -51857,7 +51856,7 @@
       <c r="O571" s="16"/>
       <c r="P571" s="16"/>
     </row>
-    <row r="572" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="572" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A572" s="15" t="s">
         <v>1902</v>
       </c>
@@ -51892,7 +51891,7 @@
       <c r="O572" s="16"/>
       <c r="P572" s="16"/>
     </row>
-    <row r="573" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="573" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A573" s="15" t="s">
         <v>1903</v>
       </c>
@@ -51927,7 +51926,7 @@
       <c r="O573" s="16"/>
       <c r="P573" s="16"/>
     </row>
-    <row r="574" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="574" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A574" s="15" t="s">
         <v>1904</v>
       </c>
@@ -51962,7 +51961,7 @@
       <c r="O574" s="16"/>
       <c r="P574" s="16"/>
     </row>
-    <row r="575" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="575" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A575" s="15" t="s">
         <v>1905</v>
       </c>
@@ -51997,7 +51996,7 @@
       <c r="O575" s="16"/>
       <c r="P575" s="16"/>
     </row>
-    <row r="576" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="576" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A576" s="15" t="s">
         <v>1906</v>
       </c>
@@ -52032,7 +52031,7 @@
       <c r="O576" s="16"/>
       <c r="P576" s="16"/>
     </row>
-    <row r="577" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="577" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A577" s="15" t="s">
         <v>1907</v>
       </c>
@@ -52067,7 +52066,7 @@
       <c r="O577" s="16"/>
       <c r="P577" s="16"/>
     </row>
-    <row r="578" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="578" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A578" s="15" t="s">
         <v>1908</v>
       </c>
@@ -52102,7 +52101,7 @@
       <c r="O578" s="16"/>
       <c r="P578" s="16"/>
     </row>
-    <row r="579" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="579" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A579" s="15" t="s">
         <v>1909</v>
       </c>
@@ -52137,7 +52136,7 @@
       <c r="O579" s="16"/>
       <c r="P579" s="16"/>
     </row>
-    <row r="580" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="580" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A580" s="15" t="s">
         <v>1910</v>
       </c>
@@ -52172,7 +52171,7 @@
       <c r="O580" s="16"/>
       <c r="P580" s="16"/>
     </row>
-    <row r="581" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="581" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A581" s="15" t="s">
         <v>1911</v>
       </c>
@@ -52207,7 +52206,7 @@
       <c r="O581" s="16"/>
       <c r="P581" s="16"/>
     </row>
-    <row r="582" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="582" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A582" s="15" t="s">
         <v>1912</v>
       </c>
@@ -52242,7 +52241,7 @@
       <c r="O582" s="16"/>
       <c r="P582" s="16"/>
     </row>
-    <row r="583" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="583" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A583" s="15" t="s">
         <v>1913</v>
       </c>
@@ -52277,7 +52276,7 @@
       <c r="O583" s="16"/>
       <c r="P583" s="16"/>
     </row>
-    <row r="584" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="584" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A584" s="15" t="s">
         <v>1914</v>
       </c>
@@ -52312,7 +52311,7 @@
       <c r="O584" s="16"/>
       <c r="P584" s="16"/>
     </row>
-    <row r="585" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="585" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A585" s="15" t="s">
         <v>1915</v>
       </c>
@@ -52347,7 +52346,7 @@
       <c r="O585" s="16"/>
       <c r="P585" s="16"/>
     </row>
-    <row r="586" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="586" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A586" s="15" t="s">
         <v>1916</v>
       </c>
@@ -52382,7 +52381,7 @@
       <c r="O586" s="16"/>
       <c r="P586" s="16"/>
     </row>
-    <row r="587" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="587" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A587" s="15" t="s">
         <v>1917</v>
       </c>
@@ -52417,7 +52416,7 @@
       <c r="O587" s="16"/>
       <c r="P587" s="16"/>
     </row>
-    <row r="588" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="588" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A588" s="15" t="s">
         <v>1918</v>
       </c>
@@ -52452,7 +52451,7 @@
       <c r="O588" s="16"/>
       <c r="P588" s="16"/>
     </row>
-    <row r="589" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="589" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A589" s="15" t="s">
         <v>1919</v>
       </c>
@@ -52487,7 +52486,7 @@
       <c r="O589" s="16"/>
       <c r="P589" s="16"/>
     </row>
-    <row r="590" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="590" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A590" s="15" t="s">
         <v>1920</v>
       </c>
@@ -52522,7 +52521,7 @@
       <c r="O590" s="16"/>
       <c r="P590" s="16"/>
     </row>
-    <row r="591" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="591" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A591" s="15" t="s">
         <v>1921</v>
       </c>
@@ -52557,7 +52556,7 @@
       <c r="O591" s="16"/>
       <c r="P591" s="16"/>
     </row>
-    <row r="592" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="592" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A592" s="15" t="s">
         <v>1922</v>
       </c>
@@ -52592,7 +52591,7 @@
       <c r="O592" s="16"/>
       <c r="P592" s="16"/>
     </row>
-    <row r="593" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="593" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A593" s="15" t="s">
         <v>1923</v>
       </c>
@@ -52627,7 +52626,7 @@
       <c r="O593" s="16"/>
       <c r="P593" s="16"/>
     </row>
-    <row r="594" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="594" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A594" s="15" t="s">
         <v>1924</v>
       </c>
@@ -52662,7 +52661,7 @@
       <c r="O594" s="16"/>
       <c r="P594" s="16"/>
     </row>
-    <row r="595" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="595" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A595" s="15" t="s">
         <v>1925</v>
       </c>
@@ -52697,7 +52696,7 @@
       <c r="O595" s="16"/>
       <c r="P595" s="16"/>
     </row>
-    <row r="596" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="596" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A596" s="15" t="s">
         <v>1926</v>
       </c>
@@ -52732,7 +52731,7 @@
       <c r="O596" s="16"/>
       <c r="P596" s="16"/>
     </row>
-    <row r="597" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="597" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A597" s="15" t="s">
         <v>1927</v>
       </c>
@@ -52767,7 +52766,7 @@
       <c r="O597" s="16"/>
       <c r="P597" s="16"/>
     </row>
-    <row r="598" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="598" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A598" s="15" t="s">
         <v>1928</v>
       </c>
@@ -52802,7 +52801,7 @@
       <c r="O598" s="16"/>
       <c r="P598" s="16"/>
     </row>
-    <row r="599" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="599" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A599" s="15" t="s">
         <v>1929</v>
       </c>
@@ -52837,7 +52836,7 @@
       <c r="O599" s="16"/>
       <c r="P599" s="16"/>
     </row>
-    <row r="600" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="600" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A600" s="15" t="s">
         <v>1930</v>
       </c>
@@ -52872,7 +52871,7 @@
       <c r="O600" s="16"/>
       <c r="P600" s="16"/>
     </row>
-    <row r="601" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="601" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A601" s="15" t="s">
         <v>1931</v>
       </c>
@@ -52907,7 +52906,7 @@
       <c r="O601" s="16"/>
       <c r="P601" s="16"/>
     </row>
-    <row r="602" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="602" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A602" s="15" t="s">
         <v>1932</v>
       </c>
@@ -52942,7 +52941,7 @@
       <c r="O602" s="16"/>
       <c r="P602" s="16"/>
     </row>
-    <row r="603" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="603" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A603" s="15" t="s">
         <v>1933</v>
       </c>
@@ -52977,7 +52976,7 @@
       <c r="O603" s="16"/>
       <c r="P603" s="16"/>
     </row>
-    <row r="604" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="604" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A604" s="15" t="s">
         <v>1934</v>
       </c>
@@ -53012,7 +53011,7 @@
       <c r="O604" s="16"/>
       <c r="P604" s="16"/>
     </row>
-    <row r="605" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="605" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A605" s="15" t="s">
         <v>1935</v>
       </c>
@@ -53047,7 +53046,7 @@
       <c r="O605" s="16"/>
       <c r="P605" s="16"/>
     </row>
-    <row r="606" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="606" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A606" s="15" t="s">
         <v>1936</v>
       </c>
@@ -53082,7 +53081,7 @@
       <c r="O606" s="16"/>
       <c r="P606" s="16"/>
     </row>
-    <row r="607" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="607" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A607" s="15" t="s">
         <v>1937</v>
       </c>
@@ -53117,7 +53116,7 @@
       <c r="O607" s="16"/>
       <c r="P607" s="16"/>
     </row>
-    <row r="608" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="608" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A608" s="15" t="s">
         <v>1938</v>
       </c>
@@ -53152,7 +53151,7 @@
       <c r="O608" s="16"/>
       <c r="P608" s="16"/>
     </row>
-    <row r="609" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="609" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A609" s="15" t="s">
         <v>1939</v>
       </c>
@@ -53187,7 +53186,7 @@
       <c r="O609" s="16"/>
       <c r="P609" s="16"/>
     </row>
-    <row r="610" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="610" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A610" s="15" t="s">
         <v>1940</v>
       </c>
@@ -53222,7 +53221,7 @@
       <c r="O610" s="16"/>
       <c r="P610" s="16"/>
     </row>
-    <row r="611" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="611" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A611" s="15" t="s">
         <v>1941</v>
       </c>
@@ -53257,7 +53256,7 @@
       <c r="O611" s="16"/>
       <c r="P611" s="16"/>
     </row>
-    <row r="612" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="612" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A612" s="15" t="s">
         <v>1942</v>
       </c>
@@ -53292,7 +53291,7 @@
       <c r="O612" s="16"/>
       <c r="P612" s="16"/>
     </row>
-    <row r="613" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="613" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A613" s="15" t="s">
         <v>1943</v>
       </c>
@@ -53327,7 +53326,7 @@
       <c r="O613" s="16"/>
       <c r="P613" s="16"/>
     </row>
-    <row r="614" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="614" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A614" s="15" t="s">
         <v>1944</v>
       </c>
@@ -53362,7 +53361,7 @@
       <c r="O614" s="16"/>
       <c r="P614" s="16"/>
     </row>
-    <row r="615" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="615" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A615" s="15" t="s">
         <v>1945</v>
       </c>
@@ -53397,7 +53396,7 @@
       <c r="O615" s="16"/>
       <c r="P615" s="16"/>
     </row>
-    <row r="616" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="616" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A616" s="15" t="s">
         <v>1946</v>
       </c>
@@ -53432,7 +53431,7 @@
       <c r="O616" s="16"/>
       <c r="P616" s="16"/>
     </row>
-    <row r="617" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="617" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A617" s="15" t="s">
         <v>1947</v>
       </c>
@@ -53467,7 +53466,7 @@
       <c r="O617" s="16"/>
       <c r="P617" s="16"/>
     </row>
-    <row r="618" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="618" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A618" s="15" t="s">
         <v>1948</v>
       </c>
@@ -53502,7 +53501,7 @@
       <c r="O618" s="16"/>
       <c r="P618" s="16"/>
     </row>
-    <row r="619" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="619" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A619" s="15" t="s">
         <v>1949</v>
       </c>
@@ -53537,7 +53536,7 @@
       <c r="O619" s="16"/>
       <c r="P619" s="16"/>
     </row>
-    <row r="620" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="620" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A620" s="15" t="s">
         <v>1950</v>
       </c>
@@ -53572,7 +53571,7 @@
       <c r="O620" s="16"/>
       <c r="P620" s="16"/>
     </row>
-    <row r="621" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="621" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A621" s="15" t="s">
         <v>1951</v>
       </c>
@@ -53607,7 +53606,7 @@
       <c r="O621" s="16"/>
       <c r="P621" s="16"/>
     </row>
-    <row r="622" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="622" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A622" s="15" t="s">
         <v>1952</v>
       </c>
@@ -53642,7 +53641,7 @@
       <c r="O622" s="16"/>
       <c r="P622" s="16"/>
     </row>
-    <row r="623" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="623" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A623" s="15" t="s">
         <v>1953</v>
       </c>
@@ -53677,7 +53676,7 @@
       <c r="O623" s="16"/>
       <c r="P623" s="16"/>
     </row>
-    <row r="624" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="624" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A624" s="15" t="s">
         <v>1954</v>
       </c>
@@ -53712,7 +53711,7 @@
       <c r="O624" s="16"/>
       <c r="P624" s="16"/>
     </row>
-    <row r="625" spans="1:16" s="14" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="625" spans="1:16" s="14" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A625" s="15" t="s">
         <v>2128</v>
       </c>
@@ -53747,7 +53746,7 @@
       <c r="O625" s="16"/>
       <c r="P625" s="16"/>
     </row>
-    <row r="626" spans="1:16" s="14" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
+    <row r="626" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A626" s="15" t="s">
         <v>2135</v>
       </c>
@@ -53784,7 +53783,7 @@
       <c r="O626" s="16"/>
       <c r="P626" s="16"/>
     </row>
-    <row r="627" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="627" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A627" s="12" t="s">
         <v>1138</v>
       </c>
@@ -53814,7 +53813,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-325','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001096','compareValue','svrBussRepAssetCreditNonstdInfoDto.repPledgeType','==','99','抵质押物类型为其他时','E');</v>
       </c>
     </row>
-    <row r="628" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="628" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A628" s="12" t="s">
         <v>909</v>
       </c>
@@ -53844,7 +53843,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-030','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001091','compareValue','svrBussRepAssetCreditNonstdInfoDto.repProfitType','==','99','当收/受益权类型为其他时','E');</v>
       </c>
     </row>
-    <row r="629" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="629" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A629" s="15" t="s">
         <v>2148</v>
       </c>
@@ -53874,7 +53873,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-795','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000385','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="630" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="630" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A630" s="15" t="s">
         <v>2159</v>
       </c>
@@ -53904,7 +53903,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-796','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000388','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="631" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="631" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A631" s="15" t="s">
         <v>2167</v>
       </c>
@@ -53934,7 +53933,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-797','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000389','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="632" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="632" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A632" s="15" t="s">
         <v>2175</v>
       </c>
@@ -53964,7 +53963,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-798','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000392','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="633" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="633" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A633" s="15" t="s">
         <v>2182</v>
       </c>
@@ -53994,7 +53993,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-799','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000393','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="634" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="634" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A634" s="15" t="s">
         <v>2190</v>
       </c>
@@ -54024,7 +54023,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-800','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000396','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="635" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="635" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A635" s="15" t="s">
         <v>2199</v>
       </c>
@@ -54054,7 +54053,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-801','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000399','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="636" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="636" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A636" s="15" t="s">
         <v>2214</v>
       </c>
@@ -54084,7 +54083,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-802','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000401','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="637" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="637" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A637" s="15" t="s">
         <v>1174</v>
       </c>
@@ -54114,7 +54113,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-411','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF3F-D920-E050-007F010077FD','compareValue','svrBussRepAssetCreditNonstdInfoDto.repRateFlag','==','01','“是否有预期收益率”选择“01 是”','E');</v>
       </c>
     </row>
-    <row r="638" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="638" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A638" s="15" t="s">
         <v>1176</v>
       </c>
@@ -54144,7 +54143,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-413','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF40-D920-E050-007F010077FD','compareValue','svrBussRepAssetCreditNonstdInfoDto.repRateFlag','==','02','“是否有预期收益率”选择“02 否”','E');</v>
       </c>
     </row>
-    <row r="639" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="639" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A639" s="15" t="s">
         <v>2236</v>
       </c>
@@ -54174,7 +54173,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-805','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000407','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="640" spans="1:16" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="640" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A640" s="15" t="s">
         <v>2240</v>
       </c>
@@ -54204,7 +54203,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-806','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000409','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="641" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="641" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A641" s="15" t="s">
         <v>2241</v>
       </c>
@@ -54234,7 +54233,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-807','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000410','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209','当资产/负债类别为非标准化债权类资产时','E');</v>
       </c>
     </row>
-    <row r="642" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="642" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A642" s="15" t="s">
         <v>1178</v>
       </c>
@@ -54294,7 +54293,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-326','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001097','compareValue','svrBussRepAssetCreditNonstdInfoDto.repRelationFinan','==','99','担保人与融资人关系为其他时','E');</v>
       </c>
     </row>
-    <row r="644" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="644" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A644" s="12" t="s">
         <v>908</v>
       </c>
@@ -54324,7 +54323,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-029','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001090','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="645" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="645" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A645" s="12" t="s">
         <v>1140</v>
       </c>
@@ -54354,7 +54353,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-327','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001180','compareValueAsNumber','svrBussRepAssetCreditNonstdInfoDto.totalFeeRate','&gt;','0','当融资总费率不为0时','E');</v>
       </c>
     </row>
-    <row r="646" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="646" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A646" s="15" t="s">
         <v>2270</v>
       </c>
@@ -54382,7 +54381,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-812','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000395','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="647" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="647" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A647" s="15" t="s">
         <v>2271</v>
       </c>
@@ -54410,7 +54409,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-813','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000397','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="648" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="648" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A648" s="15" t="s">
         <v>2272</v>
       </c>
@@ -54438,7 +54437,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-814','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000398','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="649" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="649" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A649" s="15" t="s">
         <v>2273</v>
       </c>
@@ -54466,7 +54465,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-815','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000402','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="650" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="650" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A650" s="15" t="s">
         <v>2274</v>
       </c>
@@ -54494,7 +54493,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-816','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000400','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="651" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="651" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A651" s="15" t="s">
         <v>2275</v>
       </c>
@@ -54522,7 +54521,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-817','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000391','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="652" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="652" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A652" s="15" t="s">
         <v>2276</v>
       </c>
@@ -54550,7 +54549,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-818','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000390','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="653" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="653" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A653" s="15" t="s">
         <v>2277</v>
       </c>
@@ -54578,7 +54577,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-819','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000383','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="654" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="654" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A654" s="15" t="s">
         <v>2278</v>
       </c>
@@ -54606,7 +54605,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-820','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000386','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="655" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="655" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A655" s="15" t="s">
         <v>2279</v>
       </c>
@@ -54634,7 +54633,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-821','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000415','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="656" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="656" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A656" s="15" t="s">
         <v>2280</v>
       </c>
@@ -54662,7 +54661,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-822','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000416','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="657" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="657" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A657" s="15" t="s">
         <v>2281</v>
       </c>
@@ -54690,7 +54689,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-823','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000418','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="658" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="658" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A658" s="15" t="s">
         <v>2282</v>
       </c>
@@ -54718,7 +54717,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-824','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000405','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="659" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="659" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A659" s="15" t="s">
         <v>2283</v>
       </c>
@@ -54746,7 +54745,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-825','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000412','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="660" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="660" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A660" s="15" t="s">
         <v>2284</v>
       </c>
@@ -54774,7 +54773,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-826','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000381','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="661" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="661" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A661" s="15" t="s">
         <v>2285</v>
       </c>
@@ -54802,7 +54801,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-827','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000394','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="662" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="662" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A662" s="15" t="s">
         <v>2286</v>
       </c>
@@ -54830,7 +54829,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-828','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000408','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="663" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="663" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A663" s="15" t="s">
         <v>2287</v>
       </c>
@@ -54858,7 +54857,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-829','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000387','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="664" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="664" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A664" s="15" t="s">
         <v>2288</v>
       </c>
@@ -54886,7 +54885,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-830','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000379','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="665" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="665" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A665" s="15" t="s">
         <v>2289</v>
       </c>
@@ -54914,7 +54913,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-831','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000380','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="666" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="666" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A666" s="15" t="s">
         <v>2290</v>
       </c>
@@ -54942,7 +54941,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-832','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000404','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="667" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="667" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A667" s="15" t="s">
         <v>2347</v>
       </c>
@@ -54969,7 +54968,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-833','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000419','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="668" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="668" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A668" s="15" t="s">
         <v>2348</v>
       </c>
@@ -54996,7 +54995,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-834','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000420','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="669" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="669" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A669" s="15" t="s">
         <v>2349</v>
       </c>
@@ -55023,7 +55022,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-835','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000421','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="670" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="670" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A670" s="15" t="s">
         <v>2350</v>
       </c>
@@ -55050,7 +55049,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-836','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000422','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="671" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="671" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A671" s="15" t="s">
         <v>2351</v>
       </c>
@@ -55077,7 +55076,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-837','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000423','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="672" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="672" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A672" s="15" t="s">
         <v>2352</v>
       </c>
@@ -55104,7 +55103,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-838','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000424','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A673" s="15" t="s">
         <v>2527</v>
       </c>
@@ -55131,7 +55130,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-839','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-F153-107F010077FD','inArray','assetType2','==','2403,2499,2402,1106,2401,2604,2602,2601,2617,2616,2614,2618,2699,2620,2619,2607,2606,2605,2610,2613,2612,2611,1303','','E');</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A674" s="15" t="s">
         <v>2528</v>
       </c>
@@ -55158,7 +55157,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-840','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-E050-107F110077FD','inArray','assetType2','==','1201,1210','','E');</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A675" s="15" t="s">
         <v>2529</v>
       </c>
@@ -55185,7 +55184,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-841','ASSET_INFO_DETAIL_RULE_0000-979184d8-0972-49df-a57f-bda5e1f6fafc','inArray','assetType2','==','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A676" s="15" t="s">
         <v>2530</v>
       </c>
@@ -55212,7 +55211,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-843','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-E050-107F310077FD','inArray','assetType2','==','1301,1305,1302','','E');</v>
       </c>
     </row>
-    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A677" s="15" t="s">
         <v>2531</v>
       </c>
@@ -55239,7 +55238,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-844','ASSET_INFO_DETAIL_RULE_0000-884807E5-DF1E-D920-E050-107F210077FD','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A678" s="15" t="s">
         <v>2532</v>
       </c>
@@ -55266,7 +55265,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-845','ASSET_INFO_DETAIL_RULE_0000-LZ4827E5-DF35-D920-E050-007F01001090','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A679" s="15" t="s">
         <v>2542</v>
       </c>
@@ -55293,7 +55292,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-846','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000425','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A680" s="15" t="s">
         <v>2543</v>
       </c>
@@ -55320,7 +55319,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-847','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000426','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A681" s="15" t="s">
         <v>2544</v>
       </c>
@@ -55347,7 +55346,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-848','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000427','inArray','assetType2','==','1202,1203,1204,1205,1206,1207,1208,1209,2201,2202','','E');</v>
       </c>
     </row>
-    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A682" s="15" t="s">
         <v>2553</v>
       </c>
@@ -55374,7 +55373,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-849','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000429','inArray','assetType2','==','1003,1005','','E');</v>
       </c>
     </row>
-    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A683" s="15" t="s">
         <v>2564</v>
       </c>
@@ -55401,7 +55400,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-850','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000433','inArray','assetType2','==','1002,1003,1004,1005','','E');</v>
       </c>
     </row>
-    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A684" s="15" t="s">
         <v>2567</v>
       </c>
@@ -55431,7 +55430,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-851','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000434','compareValue','svrBussRepAssetCreditNonstdInfoDto.floatFactorFlag','!=','01','当“是否有浮动因子”为“否”或为空时','E');</v>
       </c>
     </row>
-    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A685" s="15" t="s">
         <v>2571</v>
       </c>
@@ -55461,7 +55460,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-852','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000435','inArray','assetType2','==','2201,2202','当资产/负债类别为新增可投资资产时','E');</v>
       </c>
     </row>
-    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A686" s="15" t="s">
         <v>2578</v>
       </c>
@@ -55491,7 +55490,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-853','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000436','compareValue','svrBussRepAssetCreditNonstdInfoDto.repDeferredInterestType','==','01','当“递延利息条款类型”选择“01 无利息递延条款”或为空时','E');</v>
       </c>
     </row>
-    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A687" s="15" t="s">
         <v>2579</v>
       </c>
@@ -55521,7 +55520,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-854','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000437','lessThanCharLength','svrBussRepAssetCreditNonstdInfoDto.repDeferredInterestType','==','0','当“递延利息条款类型”选择“01 无利息递延条款”或为空时','E');</v>
       </c>
     </row>
-    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A688" s="15" t="s">
         <v>2590</v>
       </c>
@@ -55551,7 +55550,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-855','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000438','inArray','assetType2','==','2201,2202','当资产/负债类别为新增可投资资产时','E');</v>
       </c>
     </row>
-    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A689" s="15" t="s">
         <v>2592</v>
       </c>
@@ -55581,7 +55580,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-856','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000439','inArray','assetType2','==','1002,1003','当资产/负债类别为本行/他行存款时','E');</v>
       </c>
     </row>
-    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A690" s="15" t="s">
         <v>2598</v>
       </c>
@@ -55611,7 +55610,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-857','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000440','inArray','assetType2','==','1108,1902','当资产/负债类别为卖出回购或买入返售时','E');</v>
       </c>
     </row>
-    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A691" s="15" t="s">
         <v>2604</v>
       </c>
@@ -55641,7 +55640,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-858','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000441','inArray','assetType2','==','1108,1902','当资产/负债类别为卖出回购或买入返售时','E');</v>
       </c>
     </row>
-    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A692" s="15" t="s">
         <v>2608</v>
       </c>
@@ -55671,7 +55670,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-859','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000442','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A693" s="15" t="s">
         <v>2609</v>
       </c>
@@ -55698,7 +55697,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-860','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000442','inArray','assetType2','==','1107,1108,1901,1902','','E');</v>
       </c>
     </row>
-    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A694" s="15" t="s">
         <v>2619</v>
       </c>
@@ -55726,7 +55725,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-861','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000443','inArray','assetType2','==','1101,1110,1109,1102,1111,1112,1113,1114,1115,1116,1117,2101,2501,2502','','E');</v>
       </c>
     </row>
-    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A695" s="15" t="s">
         <v>2628</v>
       </c>
@@ -55753,7 +55752,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-862','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000444','inArray','assetType2','==','1201,1210','','E');</v>
       </c>
     </row>
-    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A696" s="15" t="s">
         <v>2634</v>
       </c>
@@ -55783,7 +55782,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-863','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000445','compareValue','svrBussRepDepositInfoDto.repDepoType','==','06','当“存款类型”要素选择“06 结构性存款”时','E');</v>
       </c>
     </row>
-    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A697" s="15" t="s">
         <v>2635</v>
       </c>
@@ -55813,7 +55812,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-864','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000446','compareValue','svrBussRepDepositInfoDto.repDepoType','==','06','当“存款类型”要素选择“06 结构性存款”时','E');</v>
       </c>
     </row>
-    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A698" s="15" t="s">
         <v>2660</v>
       </c>
@@ -55840,7 +55839,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-865','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000447','inArray','assetType2','==','1703,1704,1705,1706,1701,1702','','E');</v>
       </c>
     </row>
-    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A699" s="15" t="s">
         <v>2661</v>
       </c>
@@ -55867,7 +55866,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-866','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000448','inArray','assetType2','==','1703,1704,1705,1706,1701,1702','','E');</v>
       </c>
     </row>
-    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A700" s="15" t="s">
         <v>2662</v>
       </c>
@@ -55894,7 +55893,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-867','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000449','inArray','assetType2','==','1703,1704,1705,1706,1701,1702','','E');</v>
       </c>
     </row>
-    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A701" s="15" t="s">
         <v>2663</v>
       </c>
@@ -55921,7 +55920,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-868','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000450','inArray','assetType2','==','1703,1704,1705,1706,1701,1702','','E');</v>
       </c>
     </row>
-    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A702" s="15" t="s">
         <v>2681</v>
       </c>
@@ -55948,7 +55947,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-869','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000451','inArray','assetType2','==','1703,1704,1705,1706,1701,1702','','E');</v>
       </c>
     </row>
-    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A703" s="15" t="s">
         <v>2682</v>
       </c>
@@ -55978,7 +55977,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-870','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000451','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A704" s="15" t="s">
         <v>2683</v>
       </c>
@@ -56006,7 +56005,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-871','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000452','inArray','assetType2','==','1401,1402,1403,1404,1405,1406,1499','','E');</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A705" s="15" t="s">
         <v>2693</v>
       </c>
@@ -56033,7 +56032,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-872','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000453','inArray','assetType2','==','1401,1402,1403,1404,1405,1406,1499','','E');</v>
       </c>
     </row>
-    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A706" s="15" t="s">
         <v>2694</v>
       </c>
@@ -56063,7 +56062,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-873','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000453','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A707" s="15" t="s">
         <v>2695</v>
       </c>
@@ -56093,7 +56092,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-874','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000454','compareValue','svrBussRepFinanciallInfoDto.targetType3','==','99','当标的类别为其他时','E');</v>
       </c>
     </row>
-    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A708" s="15" t="s">
         <v>2696</v>
       </c>
@@ -56123,7 +56122,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-875','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000455','compareValue','svrBussRepFinanciallInfoDto.holdPurpose','==','99','当持有目的为其他时','E');</v>
       </c>
     </row>
-    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A709" s="15" t="s">
         <v>2711</v>
       </c>
@@ -56150,7 +56149,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-876','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000456','inArray','assetType2','==','2801,2802,2803,2804,2805,2806,2899','','E');</v>
       </c>
     </row>
-    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A710" s="15" t="s">
         <v>2712</v>
       </c>
@@ -56180,7 +56179,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-877','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000456','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A711" s="15" t="s">
         <v>2719</v>
       </c>
@@ -56207,7 +56206,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-878','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000457','inArray','assetType2','==','1501','','E');</v>
       </c>
     </row>
-    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A712" s="15" t="s">
         <v>2724</v>
       </c>
@@ -56234,7 +56233,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-879','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000458','inArray','assetType2','==','1501','','E');</v>
       </c>
     </row>
-    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A713" s="15" t="s">
         <v>2725</v>
       </c>
@@ -56261,7 +56260,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-880','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000428','inArray','assetType2','==','1002,1003,1004,1005','','E');</v>
       </c>
     </row>
-    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A714" s="15" t="s">
         <v>2726</v>
       </c>
@@ -56288,7 +56287,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-881','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000430','inArray','assetType2','==','1002,1003,1004,1005','','E');</v>
       </c>
     </row>
-    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A715" s="15" t="s">
         <v>2727</v>
       </c>
@@ -56315,7 +56314,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-882','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000431','inArray','assetType2','==','1002,1003,1004,1005','','E');</v>
       </c>
     </row>
-    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A716" s="15" t="s">
         <v>2728</v>
       </c>
@@ -56342,7 +56341,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-883','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000432','inArray','assetType2','==','1002,1003,1004,1005','','E');</v>
       </c>
     </row>
-    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A717" s="15" t="s">
         <v>2732</v>
       </c>
@@ -56369,7 +56368,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-884','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000459','inArray','assetType2','==','1501','','E');</v>
       </c>
     </row>
-    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A718" s="15" t="s">
         <v>2733</v>
       </c>
@@ -56399,7 +56398,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-885','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000459','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A719" s="15" t="s">
         <v>2737</v>
       </c>
@@ -56426,7 +56425,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-886','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000460','inArray','assetType2','==','1504,1506','','E');</v>
       </c>
     </row>
-    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A720" s="15" t="s">
         <v>2738</v>
       </c>
@@ -56456,7 +56455,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-887','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000460','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A721" s="15" t="s">
         <v>2741</v>
       </c>
@@ -56483,7 +56482,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-888','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000461','inArray','assetType2','==','1502,1505,1507,1508,1509','','E');</v>
       </c>
     </row>
-    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A722" s="15" t="s">
         <v>2742</v>
       </c>
@@ -56513,7 +56512,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-889','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000461','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A723" s="15" t="s">
         <v>2750</v>
       </c>
@@ -56540,7 +56539,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-890','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000462','inArray','assetType2','==','1503','','E');</v>
       </c>
     </row>
-    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A724" s="15" t="s">
         <v>2751</v>
       </c>
@@ -56570,7 +56569,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-891','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000462','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A725" s="15" t="s">
         <v>2758</v>
       </c>
@@ -56597,7 +56596,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-892','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000463','inArray','assetType2','==','1601,1602,1699','','E');</v>
       </c>
     </row>
-    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A726" s="15" t="s">
         <v>2759</v>
       </c>
@@ -56627,7 +56626,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-893','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000463','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A727" s="15" t="s">
         <v>2765</v>
       </c>
@@ -56654,7 +56653,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-894','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000464','inArray','assetType2','==','2301,2302,2303,2304,2305,1603','','E');</v>
       </c>
     </row>
-    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A728" s="15" t="s">
         <v>2766</v>
       </c>
@@ -56684,7 +56683,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-895','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000464','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A729" s="15" t="s">
         <v>2773</v>
       </c>
@@ -56711,7 +56710,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-896','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000465','inArray','assetType2','==','2000','','E');</v>
       </c>
     </row>
-    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A730" s="15" t="s">
         <v>2777</v>
       </c>
@@ -56738,7 +56737,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-897','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000466','inArray','assetType2','==','2000','','E');</v>
       </c>
     </row>
-    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A731" s="15" t="s">
         <v>2778</v>
       </c>
@@ -56768,7 +56767,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-898','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000466','compareValue','tradeMarket','==','99','当交易流通场所为其他交易流通场所时','E');</v>
       </c>
     </row>
-    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A732" s="15" t="s">
         <v>2795</v>
       </c>
@@ -56798,7 +56797,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-899','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000467','lessThanCharLength','svrBussRepOtherInvestTargetInfoDto.guaType','==','0','“担保方式”为空时','E');</v>
       </c>
     </row>
-    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A733" s="15" t="s">
         <v>2796</v>
       </c>
@@ -56825,7 +56824,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-900','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000467','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A734" s="15" t="s">
         <v>2810</v>
       </c>
@@ -56852,7 +56851,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-901','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000468','inArray','assetType2','==','1503','','E');</v>
       </c>
     </row>
-    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A735" s="15" t="s">
         <v>2824</v>
       </c>
@@ -56879,7 +56878,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-902','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000469','inArray','assetType2','==','1501','','E');</v>
       </c>
     </row>
-    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A736" s="15" t="s">
         <v>2830</v>
       </c>
@@ -56906,7 +56905,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-903','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000470','inArray','assetType2','==','1502,1505,1507,1508,1509','','E');</v>
       </c>
     </row>
-    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A737" s="15" t="s">
         <v>2840</v>
       </c>
@@ -56933,7 +56932,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-904','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000471','inArray','assetType2','==','1299,1399,1599,2299','','E');</v>
       </c>
     </row>
-    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A738" s="15" t="s">
         <v>2848</v>
       </c>
@@ -56960,7 +56959,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-905','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000472','inArray','assetType2','==','1399','','E');</v>
       </c>
     </row>
-    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A739" s="15" t="s">
         <v>2856</v>
       </c>
@@ -56987,7 +56986,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-906','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000473','inArray','assetType2','==','2604,2602,2601,2617,2616,2614,2618,2699,2620,2619,2607,2606,2605,2610,2613,2612,2611','','E');</v>
       </c>
     </row>
-    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A740" s="15" t="s">
         <v>2862</v>
       </c>
@@ -57014,7 +57013,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-907','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000474','inArray','assetType2','==','2403,2499,2402,1106,2401,2604,2602,2601,2617,2616,2614,2618,2699,2620,2619,2607,2606,2605,2610,2613,2612,2611,1303','','E');</v>
       </c>
     </row>
-    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A741" s="15" t="s">
         <v>2867</v>
       </c>
@@ -57041,7 +57040,7 @@
         <v>INSERT INTO CHB_DATACHECK_CONDITION_INV VALUES ('ASSET_INFO_DETAIL_CONDITION_0000-908','ASSET_INFO_DETAIL_RULE_0000-0000-0000-0000-0000-0000-0000-000475','inArray','assetType2','==','2403,2499,2402,1106,2401,2604,2602,2601,2617,2616,2614,2618,2699,2620,2619,2607,2606,2605,2610,2613,2612,2611,1303','','E');</v>
       </c>
     </row>
-    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.15">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A742" s="15" t="s">
         <v>2878</v>
       </c>
@@ -57070,14 +57069,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I742">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="担保人与融资人关系为其他时"/>
-        <filter val="融资人类型（按规模划分）为99其他"/>
-        <filter val="融资人类型（按技术领域划分）为99其他"/>
-        <filter val="融资人类型（按经济类型划分）为99其他"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A2:I655">
       <sortCondition ref="D1:D682"/>
     </sortState>
